--- a/AAII_Financials/Yearly/HMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HMY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E7" s="2">
         <v>44742</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44377</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44012</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43646</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43281</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>42916</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42551</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42185</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>41820</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41455</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41090</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40724</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2323300</v>
+        <v>2630800</v>
       </c>
       <c r="E8" s="3">
-        <v>2273600</v>
+        <v>2276800</v>
       </c>
       <c r="F8" s="3">
-        <v>1593300</v>
+        <v>2228100</v>
       </c>
       <c r="G8" s="3">
-        <v>1466200</v>
+        <v>1561400</v>
       </c>
       <c r="H8" s="3">
-        <v>1114200</v>
+        <v>1436800</v>
       </c>
       <c r="I8" s="3">
-        <v>1049500</v>
+        <v>1091900</v>
       </c>
       <c r="J8" s="3">
+        <v>1028500</v>
+      </c>
+      <c r="K8" s="3">
         <v>998800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>921000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>99700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>106900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>133900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>117500</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2041000</v>
+        <v>2109200</v>
       </c>
       <c r="E9" s="3">
-        <v>1854100</v>
+        <v>2000100</v>
       </c>
       <c r="F9" s="3">
-        <v>1409300</v>
+        <v>1817000</v>
       </c>
       <c r="G9" s="3">
-        <v>1347200</v>
+        <v>1381100</v>
       </c>
       <c r="H9" s="3">
-        <v>983500</v>
+        <v>1320300</v>
       </c>
       <c r="I9" s="3">
-        <v>972300</v>
+        <v>963800</v>
       </c>
       <c r="J9" s="3">
+        <v>952900</v>
+      </c>
+      <c r="K9" s="3">
         <v>861500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>914800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>91300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>107400</v>
-      </c>
-      <c r="N9" s="3">
-        <v>106000</v>
       </c>
       <c r="O9" s="3">
         <v>106000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3">
+        <v>106000</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>282300</v>
+        <v>521600</v>
       </c>
       <c r="E10" s="3">
-        <v>419500</v>
+        <v>276700</v>
       </c>
       <c r="F10" s="3">
-        <v>184000</v>
+        <v>411100</v>
       </c>
       <c r="G10" s="3">
-        <v>118900</v>
+        <v>180300</v>
       </c>
       <c r="H10" s="3">
-        <v>130800</v>
+        <v>116600</v>
       </c>
       <c r="I10" s="3">
-        <v>77200</v>
+        <v>128100</v>
       </c>
       <c r="J10" s="3">
+        <v>75700</v>
+      </c>
+      <c r="K10" s="3">
         <v>137300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>27800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11500</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>11700</v>
+        <v>27000</v>
       </c>
       <c r="E12" s="3">
-        <v>9600</v>
+        <v>11400</v>
       </c>
       <c r="F12" s="3">
-        <v>11200</v>
+        <v>9500</v>
       </c>
       <c r="G12" s="3">
-        <v>8100</v>
+        <v>10900</v>
       </c>
       <c r="H12" s="3">
-        <v>7400</v>
+        <v>7900</v>
       </c>
       <c r="I12" s="3">
-        <v>13100</v>
+        <v>7200</v>
       </c>
       <c r="J12" s="3">
+        <v>12900</v>
+      </c>
+      <c r="K12" s="3">
         <v>10400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3300</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,51 +960,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>244500</v>
+        <v>3300</v>
       </c>
       <c r="E14" s="3">
-        <v>73900</v>
+        <v>239600</v>
       </c>
       <c r="F14" s="3">
-        <v>6600</v>
+        <v>72500</v>
       </c>
       <c r="G14" s="3">
-        <v>222200</v>
+        <v>6500</v>
       </c>
       <c r="H14" s="3">
-        <v>301300</v>
+        <v>217700</v>
       </c>
       <c r="I14" s="3">
-        <v>102200</v>
+        <v>295300</v>
       </c>
       <c r="J14" s="3">
+        <v>100100</v>
+      </c>
+      <c r="K14" s="3">
         <v>-1500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>222100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>10500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>17100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4200</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2364400</v>
+        <v>2263500</v>
       </c>
       <c r="E17" s="3">
-        <v>1912500</v>
+        <v>2317100</v>
       </c>
       <c r="F17" s="3">
-        <v>1615200</v>
+        <v>1874200</v>
       </c>
       <c r="G17" s="3">
-        <v>1604400</v>
+        <v>1582900</v>
       </c>
       <c r="H17" s="3">
-        <v>1373400</v>
+        <v>1572300</v>
       </c>
       <c r="I17" s="3">
-        <v>1058200</v>
+        <v>1346000</v>
       </c>
       <c r="J17" s="3">
+        <v>1037000</v>
+      </c>
+      <c r="K17" s="3">
         <v>912100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1230900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>109200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>118900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>115800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>117300</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-41100</v>
+        <v>367300</v>
       </c>
       <c r="E18" s="3">
-        <v>361100</v>
+        <v>-40300</v>
       </c>
       <c r="F18" s="3">
-        <v>-22000</v>
+        <v>353900</v>
       </c>
       <c r="G18" s="3">
-        <v>-138300</v>
+        <v>-21500</v>
       </c>
       <c r="H18" s="3">
-        <v>-259200</v>
+        <v>-135500</v>
       </c>
       <c r="I18" s="3">
-        <v>-8700</v>
+        <v>-254000</v>
       </c>
       <c r="J18" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="K18" s="3">
         <v>86700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-309900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-12000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>18100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>200</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-5900</v>
+        <v>5300</v>
       </c>
       <c r="E20" s="3">
-        <v>-2200</v>
+        <v>-5800</v>
       </c>
       <c r="F20" s="3">
-        <v>9700</v>
+        <v>-1400</v>
       </c>
       <c r="G20" s="3">
+        <v>9500</v>
+      </c>
+      <c r="H20" s="3">
         <v>3300</v>
       </c>
-      <c r="H20" s="3">
-        <v>20800</v>
-      </c>
       <c r="I20" s="3">
-        <v>13400</v>
+        <v>20300</v>
       </c>
       <c r="J20" s="3">
+        <v>13100</v>
+      </c>
+      <c r="K20" s="3">
         <v>14300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6400</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>155600</v>
+        <v>558600</v>
       </c>
       <c r="E21" s="3">
-        <v>572200</v>
+        <v>152200</v>
       </c>
       <c r="F21" s="3">
-        <v>180800</v>
+        <v>561200</v>
       </c>
       <c r="G21" s="3">
-        <v>88100</v>
+        <v>176900</v>
       </c>
       <c r="H21" s="3">
-        <v>-97100</v>
+        <v>86000</v>
       </c>
       <c r="I21" s="3">
-        <v>143300</v>
+        <v>-95300</v>
       </c>
       <c r="J21" s="3">
+        <v>140200</v>
+      </c>
+      <c r="K21" s="3">
         <v>220500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-150900</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>36000</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>10600</v>
+        <v>19900</v>
       </c>
       <c r="E22" s="3">
-        <v>11200</v>
+        <v>10400</v>
       </c>
       <c r="F22" s="3">
-        <v>20200</v>
+        <v>11700</v>
       </c>
       <c r="G22" s="3">
-        <v>14700</v>
+        <v>19800</v>
       </c>
       <c r="H22" s="3">
-        <v>18000</v>
+        <v>14400</v>
       </c>
       <c r="I22" s="3">
-        <v>12700</v>
+        <v>17600</v>
       </c>
       <c r="J22" s="3">
+        <v>12500</v>
+      </c>
+      <c r="K22" s="3">
         <v>14900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>15800</v>
-      </c>
-      <c r="L22" s="3">
-        <v>700</v>
       </c>
       <c r="M22" s="3">
         <v>700</v>
       </c>
       <c r="N22" s="3">
+        <v>700</v>
+      </c>
+      <c r="O22" s="3">
         <v>1300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4300</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-57600</v>
+        <v>352700</v>
       </c>
       <c r="E23" s="3">
-        <v>347700</v>
+        <v>-56500</v>
       </c>
       <c r="F23" s="3">
-        <v>-32400</v>
+        <v>340700</v>
       </c>
       <c r="G23" s="3">
-        <v>-149600</v>
+        <v>-31800</v>
       </c>
       <c r="H23" s="3">
-        <v>-256400</v>
+        <v>-146600</v>
       </c>
       <c r="I23" s="3">
-        <v>-8100</v>
+        <v>-251300</v>
       </c>
       <c r="J23" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="K23" s="3">
         <v>86100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-312700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-11300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>17100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2300</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2500</v>
       </c>
-      <c r="E24" s="3">
-        <v>68500</v>
-      </c>
       <c r="F24" s="3">
-        <v>13900</v>
+        <v>67200</v>
       </c>
       <c r="G24" s="3">
-        <v>-7600</v>
+        <v>13600</v>
       </c>
       <c r="H24" s="3">
-        <v>-12700</v>
+        <v>-7400</v>
       </c>
       <c r="I24" s="3">
-        <v>-27800</v>
+        <v>-12500</v>
       </c>
       <c r="J24" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="K24" s="3">
         <v>34400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-42000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3900</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-55100</v>
+        <v>260700</v>
       </c>
       <c r="E26" s="3">
-        <v>279200</v>
+        <v>-54000</v>
       </c>
       <c r="F26" s="3">
-        <v>-46300</v>
+        <v>273600</v>
       </c>
       <c r="G26" s="3">
-        <v>-142000</v>
+        <v>-45400</v>
       </c>
       <c r="H26" s="3">
-        <v>-243700</v>
+        <v>-139200</v>
       </c>
       <c r="I26" s="3">
-        <v>19700</v>
+        <v>-238800</v>
       </c>
       <c r="J26" s="3">
+        <v>19300</v>
+      </c>
+      <c r="K26" s="3">
         <v>51700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-270700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6200</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-57300</v>
+        <v>257300</v>
       </c>
       <c r="E27" s="3">
-        <v>277100</v>
+        <v>-56200</v>
       </c>
       <c r="F27" s="3">
-        <v>-47800</v>
+        <v>271600</v>
       </c>
       <c r="G27" s="3">
-        <v>-142000</v>
+        <v>-46900</v>
       </c>
       <c r="H27" s="3">
-        <v>-243700</v>
+        <v>-139200</v>
       </c>
       <c r="I27" s="3">
-        <v>19700</v>
+        <v>-238800</v>
       </c>
       <c r="J27" s="3">
+        <v>19300</v>
+      </c>
+      <c r="K27" s="3">
         <v>51700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-270700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6200</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1557,17 +1617,20 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>2100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>5100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-100</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>5900</v>
+        <v>-5300</v>
       </c>
       <c r="E32" s="3">
-        <v>2200</v>
+        <v>5800</v>
       </c>
       <c r="F32" s="3">
-        <v>-9700</v>
+        <v>1400</v>
       </c>
       <c r="G32" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="H32" s="3">
         <v>-3300</v>
       </c>
-      <c r="H32" s="3">
-        <v>-20800</v>
-      </c>
       <c r="I32" s="3">
-        <v>-13400</v>
+        <v>-20300</v>
       </c>
       <c r="J32" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-14300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6400</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-57300</v>
+        <v>257300</v>
       </c>
       <c r="E33" s="3">
-        <v>277100</v>
+        <v>-56200</v>
       </c>
       <c r="F33" s="3">
-        <v>-47800</v>
+        <v>271600</v>
       </c>
       <c r="G33" s="3">
-        <v>-142000</v>
+        <v>-46900</v>
       </c>
       <c r="H33" s="3">
-        <v>-243700</v>
+        <v>-139200</v>
       </c>
       <c r="I33" s="3">
-        <v>19700</v>
+        <v>-238800</v>
       </c>
       <c r="J33" s="3">
+        <v>19300</v>
+      </c>
+      <c r="K33" s="3">
         <v>51700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-270700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>23400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6100</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-57300</v>
+        <v>257300</v>
       </c>
       <c r="E35" s="3">
-        <v>277100</v>
+        <v>-56200</v>
       </c>
       <c r="F35" s="3">
-        <v>-47800</v>
+        <v>271600</v>
       </c>
       <c r="G35" s="3">
-        <v>-142000</v>
+        <v>-46900</v>
       </c>
       <c r="H35" s="3">
-        <v>-243700</v>
+        <v>-139200</v>
       </c>
       <c r="I35" s="3">
-        <v>19700</v>
+        <v>-238800</v>
       </c>
       <c r="J35" s="3">
+        <v>19300</v>
+      </c>
+      <c r="K35" s="3">
         <v>51700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-270700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>23400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6100</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E38" s="2">
         <v>44742</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44377</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44012</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43646</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43281</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>42916</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42551</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42185</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>41820</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41455</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41090</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40724</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>133400</v>
+        <v>153100</v>
       </c>
       <c r="E41" s="3">
-        <v>153600</v>
+        <v>130700</v>
       </c>
       <c r="F41" s="3">
-        <v>346300</v>
+        <v>150500</v>
       </c>
       <c r="G41" s="3">
-        <v>54100</v>
+        <v>339400</v>
       </c>
       <c r="H41" s="3">
-        <v>38500</v>
+        <v>53000</v>
       </c>
       <c r="I41" s="3">
-        <v>67900</v>
+        <v>37700</v>
       </c>
       <c r="J41" s="3">
+        <v>66500</v>
+      </c>
+      <c r="K41" s="3">
         <v>68400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>63700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7200</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1984,303 +2073,327 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>82900</v>
+        <v>117800</v>
       </c>
       <c r="E43" s="3">
-        <v>82900</v>
+        <v>81300</v>
       </c>
       <c r="F43" s="3">
-        <v>67000</v>
+        <v>81200</v>
       </c>
       <c r="G43" s="3">
-        <v>54300</v>
+        <v>65600</v>
       </c>
       <c r="H43" s="3">
-        <v>57900</v>
+        <v>53200</v>
       </c>
       <c r="I43" s="3">
-        <v>50700</v>
+        <v>56800</v>
       </c>
       <c r="J43" s="3">
+        <v>49700</v>
+      </c>
+      <c r="K43" s="3">
         <v>34000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>43100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>21500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12300</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>153500</v>
+        <v>174300</v>
       </c>
       <c r="E44" s="3">
-        <v>138500</v>
+        <v>150500</v>
       </c>
       <c r="F44" s="3">
-        <v>131900</v>
+        <v>135700</v>
       </c>
       <c r="G44" s="3">
-        <v>107200</v>
+        <v>129300</v>
       </c>
       <c r="H44" s="3">
-        <v>95800</v>
+        <v>105000</v>
       </c>
       <c r="I44" s="3">
-        <v>61400</v>
+        <v>93900</v>
       </c>
       <c r="J44" s="3">
+        <v>60200</v>
+      </c>
+      <c r="K44" s="3">
         <v>63600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>77100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8800</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>38500</v>
+        <v>18200</v>
       </c>
       <c r="E45" s="3">
-        <v>90900</v>
+        <v>37700</v>
       </c>
       <c r="F45" s="3">
-        <v>8700</v>
+        <v>89100</v>
       </c>
       <c r="G45" s="3">
+        <v>8500</v>
+      </c>
+      <c r="H45" s="3">
+        <v>22400</v>
+      </c>
+      <c r="I45" s="3">
+        <v>34900</v>
+      </c>
+      <c r="J45" s="3">
+        <v>87100</v>
+      </c>
+      <c r="K45" s="3">
         <v>22900</v>
       </c>
-      <c r="H45" s="3">
-        <v>35600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>88900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>22900</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3300</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>408300</v>
+        <v>463300</v>
       </c>
       <c r="E46" s="3">
-        <v>465900</v>
+        <v>400100</v>
       </c>
       <c r="F46" s="3">
-        <v>553800</v>
+        <v>456500</v>
       </c>
       <c r="G46" s="3">
-        <v>238500</v>
+        <v>542800</v>
       </c>
       <c r="H46" s="3">
-        <v>227800</v>
+        <v>233700</v>
       </c>
       <c r="I46" s="3">
-        <v>268900</v>
+        <v>223200</v>
       </c>
       <c r="J46" s="3">
+        <v>263500</v>
+      </c>
+      <c r="K46" s="3">
         <v>189000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>188000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>27500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>28500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>46400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31500</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>27200</v>
+        <v>23700</v>
       </c>
       <c r="E47" s="3">
-        <v>25000</v>
+        <v>26600</v>
       </c>
       <c r="F47" s="3">
-        <v>29100</v>
+        <v>24500</v>
       </c>
       <c r="G47" s="3">
-        <v>24200</v>
+        <v>28500</v>
       </c>
       <c r="H47" s="3">
-        <v>19000</v>
+        <v>23700</v>
       </c>
       <c r="I47" s="3">
-        <v>12800</v>
+        <v>18600</v>
       </c>
       <c r="J47" s="3">
+        <v>12500</v>
+      </c>
+      <c r="K47" s="3">
         <v>9600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5100</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2100</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1790900</v>
+        <v>2216100</v>
       </c>
       <c r="E48" s="3">
-        <v>1830400</v>
+        <v>1755000</v>
       </c>
       <c r="F48" s="3">
-        <v>1590100</v>
+        <v>1793700</v>
       </c>
       <c r="G48" s="3">
-        <v>1511800</v>
+        <v>1558200</v>
       </c>
       <c r="H48" s="3">
-        <v>1688900</v>
+        <v>1481500</v>
       </c>
       <c r="I48" s="3">
-        <v>1636800</v>
+        <v>1655100</v>
       </c>
       <c r="J48" s="3">
+        <v>1604000</v>
+      </c>
+      <c r="K48" s="3">
         <v>1630000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1763100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>205000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>194900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>548700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>326300</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E49" s="3">
         <v>2600</v>
       </c>
-      <c r="E49" s="3">
-        <v>19900</v>
-      </c>
       <c r="F49" s="3">
-        <v>29200</v>
+        <v>19500</v>
       </c>
       <c r="G49" s="3">
-        <v>29000</v>
+        <v>28600</v>
       </c>
       <c r="H49" s="3">
-        <v>28100</v>
+        <v>28500</v>
       </c>
       <c r="I49" s="3">
-        <v>32900</v>
+        <v>27500</v>
       </c>
       <c r="J49" s="3">
+        <v>32200</v>
+      </c>
+      <c r="K49" s="3">
         <v>47400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>52800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>22700</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>321200</v>
+        <v>351300</v>
       </c>
       <c r="E52" s="3">
-        <v>317700</v>
+        <v>314700</v>
       </c>
       <c r="F52" s="3">
-        <v>232600</v>
+        <v>311400</v>
       </c>
       <c r="G52" s="3">
-        <v>197900</v>
+        <v>228000</v>
       </c>
       <c r="H52" s="3">
-        <v>189500</v>
+        <v>194000</v>
       </c>
       <c r="I52" s="3">
-        <v>167000</v>
+        <v>185700</v>
       </c>
       <c r="J52" s="3">
+        <v>163700</v>
+      </c>
+      <c r="K52" s="3">
         <v>141400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>147300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>13400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>20200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>33900</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2550100</v>
+        <v>3056000</v>
       </c>
       <c r="E54" s="3">
-        <v>2658800</v>
+        <v>2499100</v>
       </c>
       <c r="F54" s="3">
-        <v>2434800</v>
+        <v>2605600</v>
       </c>
       <c r="G54" s="3">
-        <v>2001400</v>
+        <v>2386100</v>
       </c>
       <c r="H54" s="3">
-        <v>2153200</v>
+        <v>1961300</v>
       </c>
       <c r="I54" s="3">
-        <v>2118300</v>
+        <v>2110100</v>
       </c>
       <c r="J54" s="3">
+        <v>2076000</v>
+      </c>
+      <c r="K54" s="3">
         <v>2017400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2156300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>253400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>250800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>360700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>416400</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>69000</v>
+        <v>64300</v>
       </c>
       <c r="E57" s="3">
-        <v>69100</v>
+        <v>67600</v>
       </c>
       <c r="F57" s="3">
-        <v>38500</v>
+        <v>67800</v>
       </c>
       <c r="G57" s="3">
-        <v>41600</v>
+        <v>37700</v>
       </c>
       <c r="H57" s="3">
-        <v>32000</v>
+        <v>40700</v>
       </c>
       <c r="I57" s="3">
-        <v>28400</v>
+        <v>31300</v>
       </c>
       <c r="J57" s="3">
+        <v>27800</v>
+      </c>
+      <c r="K57" s="3">
         <v>19200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>31300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3700</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>12100</v>
+        <v>17000</v>
       </c>
       <c r="E58" s="3">
-        <v>26900</v>
+        <v>11900</v>
       </c>
       <c r="F58" s="3">
-        <v>17200</v>
+        <v>26400</v>
       </c>
       <c r="G58" s="3">
+        <v>16800</v>
+      </c>
+      <c r="H58" s="3">
         <v>4800</v>
       </c>
-      <c r="H58" s="3">
-        <v>37600</v>
-      </c>
       <c r="I58" s="3">
-        <v>99900</v>
+        <v>36800</v>
       </c>
       <c r="J58" s="3">
+        <v>97900</v>
+      </c>
+      <c r="K58" s="3">
         <v>16300</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="L58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>1700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3500</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>190000</v>
+        <v>285300</v>
       </c>
       <c r="E59" s="3">
-        <v>206500</v>
+        <v>186200</v>
       </c>
       <c r="F59" s="3">
-        <v>356200</v>
+        <v>202300</v>
       </c>
       <c r="G59" s="3">
-        <v>129800</v>
+        <v>349100</v>
       </c>
       <c r="H59" s="3">
-        <v>126500</v>
+        <v>127200</v>
       </c>
       <c r="I59" s="3">
-        <v>81100</v>
+        <v>124000</v>
       </c>
       <c r="J59" s="3">
+        <v>79500</v>
+      </c>
+      <c r="K59" s="3">
         <v>75100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>67800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14700</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>271000</v>
+        <v>366600</v>
       </c>
       <c r="E60" s="3">
-        <v>302500</v>
+        <v>265600</v>
       </c>
       <c r="F60" s="3">
-        <v>411900</v>
+        <v>296500</v>
       </c>
       <c r="G60" s="3">
-        <v>176200</v>
+        <v>403600</v>
       </c>
       <c r="H60" s="3">
-        <v>196100</v>
+        <v>172700</v>
       </c>
       <c r="I60" s="3">
-        <v>209400</v>
+        <v>192200</v>
       </c>
       <c r="J60" s="3">
+        <v>205200</v>
+      </c>
+      <c r="K60" s="3">
         <v>110600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>99100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21900</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>186600</v>
+        <v>315100</v>
       </c>
       <c r="E61" s="3">
-        <v>170400</v>
+        <v>182900</v>
       </c>
       <c r="F61" s="3">
-        <v>411000</v>
+        <v>167000</v>
       </c>
       <c r="G61" s="3">
-        <v>317400</v>
+        <v>402800</v>
       </c>
       <c r="H61" s="3">
-        <v>268300</v>
+        <v>311100</v>
       </c>
       <c r="I61" s="3">
-        <v>16300</v>
+        <v>262900</v>
       </c>
       <c r="J61" s="3">
+        <v>16000</v>
+      </c>
+      <c r="K61" s="3">
         <v>111100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>202800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>17800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12800</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>451700</v>
+        <v>512100</v>
       </c>
       <c r="E62" s="3">
-        <v>485300</v>
+        <v>442700</v>
       </c>
       <c r="F62" s="3">
-        <v>338500</v>
+        <v>475600</v>
       </c>
       <c r="G62" s="3">
-        <v>275800</v>
+        <v>331700</v>
       </c>
       <c r="H62" s="3">
-        <v>306100</v>
+        <v>270300</v>
       </c>
       <c r="I62" s="3">
-        <v>296900</v>
+        <v>299900</v>
       </c>
       <c r="J62" s="3">
+        <v>290900</v>
+      </c>
+      <c r="K62" s="3">
         <v>260500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>258000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>31800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>31200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>43200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>66600</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>913600</v>
+        <v>1200400</v>
       </c>
       <c r="E66" s="3">
-        <v>961200</v>
+        <v>895300</v>
       </c>
       <c r="F66" s="3">
-        <v>1161600</v>
+        <v>942000</v>
       </c>
       <c r="G66" s="3">
-        <v>769400</v>
+        <v>1138300</v>
       </c>
       <c r="H66" s="3">
-        <v>770400</v>
+        <v>754000</v>
       </c>
       <c r="I66" s="3">
-        <v>522600</v>
+        <v>755000</v>
       </c>
       <c r="J66" s="3">
+        <v>512100</v>
+      </c>
+      <c r="K66" s="3">
         <v>482200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>559900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>61000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>58800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>76100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>101300</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-374200</v>
+        <v>-110600</v>
       </c>
       <c r="E72" s="3">
-        <v>-302100</v>
+        <v>-366700</v>
       </c>
       <c r="F72" s="3">
-        <v>-550900</v>
+        <v>-296100</v>
       </c>
       <c r="G72" s="3">
-        <v>-513500</v>
+        <v>-539900</v>
       </c>
       <c r="H72" s="3">
-        <v>-384000</v>
+        <v>-503200</v>
       </c>
       <c r="I72" s="3">
-        <v>-152800</v>
+        <v>-376300</v>
       </c>
       <c r="J72" s="3">
+        <v>-149800</v>
+      </c>
+      <c r="K72" s="3">
         <v>-168800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-260800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>29500</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1636500</v>
+        <v>1855700</v>
       </c>
       <c r="E76" s="3">
-        <v>1697600</v>
+        <v>1603800</v>
       </c>
       <c r="F76" s="3">
-        <v>1273300</v>
+        <v>1663600</v>
       </c>
       <c r="G76" s="3">
-        <v>1232000</v>
+        <v>1247800</v>
       </c>
       <c r="H76" s="3">
-        <v>1382800</v>
+        <v>1207400</v>
       </c>
       <c r="I76" s="3">
-        <v>1595800</v>
+        <v>1355100</v>
       </c>
       <c r="J76" s="3">
+        <v>1563800</v>
+      </c>
+      <c r="K76" s="3">
         <v>1535200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1596400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>192400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>191900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>284600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>315100</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E80" s="2">
         <v>44742</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44377</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44012</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43646</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43281</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>42916</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42551</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42185</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>41820</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41455</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41090</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40724</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-57300</v>
+        <v>257300</v>
       </c>
       <c r="E81" s="3">
-        <v>277100</v>
+        <v>-56200</v>
       </c>
       <c r="F81" s="3">
-        <v>-47800</v>
+        <v>271600</v>
       </c>
       <c r="G81" s="3">
-        <v>-142000</v>
+        <v>-46900</v>
       </c>
       <c r="H81" s="3">
-        <v>-243700</v>
+        <v>-139200</v>
       </c>
       <c r="I81" s="3">
-        <v>19700</v>
+        <v>-238800</v>
       </c>
       <c r="J81" s="3">
+        <v>19300</v>
+      </c>
+      <c r="K81" s="3">
         <v>51700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-270700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>23400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6100</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200600</v>
+        <v>184400</v>
       </c>
       <c r="E83" s="3">
-        <v>211200</v>
+        <v>196600</v>
       </c>
       <c r="F83" s="3">
-        <v>191100</v>
+        <v>207000</v>
       </c>
       <c r="G83" s="3">
-        <v>220900</v>
+        <v>187300</v>
       </c>
       <c r="H83" s="3">
-        <v>140000</v>
+        <v>216400</v>
       </c>
       <c r="I83" s="3">
         <v>137200</v>
       </c>
       <c r="J83" s="3">
+        <v>134500</v>
+      </c>
+      <c r="K83" s="3">
         <v>118200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>147500</v>
       </c>
-      <c r="L83" s="3" t="s">
+      <c r="M83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>17500</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>377200</v>
+        <v>531100</v>
       </c>
       <c r="E89" s="3">
-        <v>500100</v>
+        <v>369700</v>
       </c>
       <c r="F89" s="3">
-        <v>257300</v>
+        <v>490100</v>
       </c>
       <c r="G89" s="3">
-        <v>254900</v>
+        <v>252200</v>
       </c>
       <c r="H89" s="3">
-        <v>211600</v>
+        <v>249800</v>
       </c>
       <c r="I89" s="3">
-        <v>207200</v>
+        <v>207400</v>
       </c>
       <c r="J89" s="3">
+        <v>203100</v>
+      </c>
+      <c r="K89" s="3">
         <v>245900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>119700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>14400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>19400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>37400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>24100</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-338500</v>
+        <v>-407900</v>
       </c>
       <c r="E91" s="3">
-        <v>-280100</v>
+        <v>-331800</v>
       </c>
       <c r="F91" s="3">
-        <v>-196200</v>
+        <v>-274500</v>
       </c>
       <c r="G91" s="3">
-        <v>-274300</v>
+        <v>-192300</v>
       </c>
       <c r="H91" s="3">
-        <v>-248500</v>
+        <v>-268800</v>
       </c>
       <c r="I91" s="3">
-        <v>-211900</v>
+        <v>-243600</v>
       </c>
       <c r="J91" s="3">
+        <v>-207700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-132800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-168400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-31900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-337800</v>
+        <v>-565700</v>
       </c>
       <c r="E94" s="3">
-        <v>-461100</v>
+        <v>-331000</v>
       </c>
       <c r="F94" s="3">
-        <v>-193800</v>
+        <v>-451900</v>
       </c>
       <c r="G94" s="3">
-        <v>-261300</v>
+        <v>-190000</v>
       </c>
       <c r="H94" s="3">
-        <v>-439900</v>
+        <v>-256100</v>
       </c>
       <c r="I94" s="3">
-        <v>-184300</v>
+        <v>-431100</v>
       </c>
       <c r="J94" s="3">
+        <v>-180600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-141600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-173500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-25400</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,32 +4220,33 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="F96" s="3">
+        <v>-36500</v>
+      </c>
+      <c r="G96" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="J96" s="3">
         <v>-23400</v>
       </c>
-      <c r="E96" s="3">
-        <v>-37300</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-23900</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -4021,17 +4254,20 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-3000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2100</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-62700</v>
+        <v>63700</v>
       </c>
       <c r="E100" s="3">
-        <v>-234200</v>
+        <v>-61500</v>
       </c>
       <c r="F100" s="3">
-        <v>234500</v>
+        <v>-229500</v>
       </c>
       <c r="G100" s="3">
-        <v>20700</v>
+        <v>229800</v>
       </c>
       <c r="H100" s="3">
-        <v>202800</v>
+        <v>20300</v>
       </c>
       <c r="I100" s="3">
-        <v>-24500</v>
+        <v>198800</v>
       </c>
       <c r="J100" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-95100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1700</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>3100</v>
+        <v>-6800</v>
       </c>
       <c r="E101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F101" s="3">
         <v>2500</v>
       </c>
-      <c r="F101" s="3">
-        <v>-5800</v>
-      </c>
       <c r="G101" s="3">
-        <v>1400</v>
+        <v>-5700</v>
       </c>
       <c r="H101" s="3">
-        <v>-3900</v>
+        <v>1300</v>
       </c>
       <c r="I101" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2400</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-20200</v>
+        <v>22400</v>
       </c>
       <c r="E102" s="3">
-        <v>-192800</v>
+        <v>-19800</v>
       </c>
       <c r="F102" s="3">
-        <v>292200</v>
+        <v>-188900</v>
       </c>
       <c r="G102" s="3">
-        <v>15600</v>
+        <v>286400</v>
       </c>
       <c r="H102" s="3">
-        <v>-29400</v>
+        <v>15300</v>
       </c>
       <c r="I102" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-45500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>100</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HMY_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2630800</v>
+        <v>2681500</v>
       </c>
       <c r="E8" s="3">
-        <v>2276800</v>
+        <v>2320700</v>
       </c>
       <c r="F8" s="3">
-        <v>2228100</v>
+        <v>2271100</v>
       </c>
       <c r="G8" s="3">
-        <v>1561400</v>
+        <v>1591500</v>
       </c>
       <c r="H8" s="3">
-        <v>1436800</v>
+        <v>1464600</v>
       </c>
       <c r="I8" s="3">
-        <v>1091900</v>
+        <v>1113000</v>
       </c>
       <c r="J8" s="3">
-        <v>1028500</v>
+        <v>1048300</v>
       </c>
       <c r="K8" s="3">
         <v>998800</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2109200</v>
+        <v>2149900</v>
       </c>
       <c r="E9" s="3">
-        <v>2000100</v>
+        <v>2038700</v>
       </c>
       <c r="F9" s="3">
-        <v>1817000</v>
+        <v>1852100</v>
       </c>
       <c r="G9" s="3">
-        <v>1381100</v>
+        <v>1407700</v>
       </c>
       <c r="H9" s="3">
-        <v>1320300</v>
+        <v>1345800</v>
       </c>
       <c r="I9" s="3">
-        <v>963800</v>
+        <v>982400</v>
       </c>
       <c r="J9" s="3">
-        <v>952900</v>
+        <v>971200</v>
       </c>
       <c r="K9" s="3">
         <v>861500</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>521600</v>
+        <v>531700</v>
       </c>
       <c r="E10" s="3">
-        <v>276700</v>
+        <v>282000</v>
       </c>
       <c r="F10" s="3">
-        <v>411100</v>
+        <v>419000</v>
       </c>
       <c r="G10" s="3">
-        <v>180300</v>
+        <v>183800</v>
       </c>
       <c r="H10" s="3">
-        <v>116600</v>
+        <v>118800</v>
       </c>
       <c r="I10" s="3">
-        <v>128100</v>
+        <v>130600</v>
       </c>
       <c r="J10" s="3">
-        <v>75700</v>
+        <v>77100</v>
       </c>
       <c r="K10" s="3">
         <v>137300</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>27000</v>
+        <v>27500</v>
       </c>
       <c r="E12" s="3">
-        <v>11400</v>
+        <v>11600</v>
       </c>
       <c r="F12" s="3">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="G12" s="3">
-        <v>10900</v>
+        <v>11200</v>
       </c>
       <c r="H12" s="3">
-        <v>7900</v>
+        <v>8100</v>
       </c>
       <c r="I12" s="3">
-        <v>7200</v>
+        <v>7300</v>
       </c>
       <c r="J12" s="3">
-        <v>12900</v>
+        <v>13100</v>
       </c>
       <c r="K12" s="3">
         <v>10400</v>
@@ -973,22 +973,22 @@
         <v>3300</v>
       </c>
       <c r="E14" s="3">
-        <v>239600</v>
+        <v>244200</v>
       </c>
       <c r="F14" s="3">
-        <v>72500</v>
+        <v>73800</v>
       </c>
       <c r="G14" s="3">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="H14" s="3">
-        <v>217700</v>
+        <v>221900</v>
       </c>
       <c r="I14" s="3">
-        <v>295300</v>
+        <v>301000</v>
       </c>
       <c r="J14" s="3">
-        <v>100100</v>
+        <v>102000</v>
       </c>
       <c r="K14" s="3">
         <v>-1500</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2263500</v>
+        <v>2307100</v>
       </c>
       <c r="E17" s="3">
-        <v>2317100</v>
+        <v>2361800</v>
       </c>
       <c r="F17" s="3">
-        <v>1874200</v>
+        <v>1910400</v>
       </c>
       <c r="G17" s="3">
-        <v>1582900</v>
+        <v>1613400</v>
       </c>
       <c r="H17" s="3">
-        <v>1572300</v>
+        <v>1602700</v>
       </c>
       <c r="I17" s="3">
-        <v>1346000</v>
+        <v>1371900</v>
       </c>
       <c r="J17" s="3">
-        <v>1037000</v>
+        <v>1057100</v>
       </c>
       <c r="K17" s="3">
         <v>912100</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>367300</v>
+        <v>374400</v>
       </c>
       <c r="E18" s="3">
-        <v>-40300</v>
+        <v>-41100</v>
       </c>
       <c r="F18" s="3">
-        <v>353900</v>
+        <v>360800</v>
       </c>
       <c r="G18" s="3">
-        <v>-21500</v>
+        <v>-21900</v>
       </c>
       <c r="H18" s="3">
-        <v>-135500</v>
+        <v>-138100</v>
       </c>
       <c r="I18" s="3">
-        <v>-254000</v>
+        <v>-258900</v>
       </c>
       <c r="J18" s="3">
-        <v>-8500</v>
+        <v>-8700</v>
       </c>
       <c r="K18" s="3">
         <v>86700</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="E20" s="3">
-        <v>-5800</v>
+        <v>-5900</v>
       </c>
       <c r="F20" s="3">
-        <v>-1400</v>
+        <v>-1500</v>
       </c>
       <c r="G20" s="3">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="H20" s="3">
         <v>3300</v>
       </c>
       <c r="I20" s="3">
-        <v>20300</v>
+        <v>20700</v>
       </c>
       <c r="J20" s="3">
-        <v>13100</v>
+        <v>13400</v>
       </c>
       <c r="K20" s="3">
         <v>14300</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>558600</v>
+        <v>565500</v>
       </c>
       <c r="E21" s="3">
-        <v>152200</v>
+        <v>151100</v>
       </c>
       <c r="F21" s="3">
-        <v>561200</v>
+        <v>567700</v>
       </c>
       <c r="G21" s="3">
-        <v>176900</v>
+        <v>176400</v>
       </c>
       <c r="H21" s="3">
-        <v>86000</v>
+        <v>83200</v>
       </c>
       <c r="I21" s="3">
-        <v>-95300</v>
+        <v>-100000</v>
       </c>
       <c r="J21" s="3">
-        <v>140200</v>
+        <v>140100</v>
       </c>
       <c r="K21" s="3">
         <v>220500</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>19900</v>
+        <v>20300</v>
       </c>
       <c r="E22" s="3">
-        <v>10400</v>
+        <v>10600</v>
       </c>
       <c r="F22" s="3">
-        <v>11700</v>
+        <v>12000</v>
       </c>
       <c r="G22" s="3">
-        <v>19800</v>
+        <v>20100</v>
       </c>
       <c r="H22" s="3">
-        <v>14400</v>
+        <v>14600</v>
       </c>
       <c r="I22" s="3">
-        <v>17600</v>
+        <v>18000</v>
       </c>
       <c r="J22" s="3">
-        <v>12500</v>
+        <v>12700</v>
       </c>
       <c r="K22" s="3">
         <v>14900</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>352700</v>
+        <v>359500</v>
       </c>
       <c r="E23" s="3">
-        <v>-56500</v>
+        <v>-57600</v>
       </c>
       <c r="F23" s="3">
-        <v>340700</v>
+        <v>347300</v>
       </c>
       <c r="G23" s="3">
-        <v>-31800</v>
+        <v>-32400</v>
       </c>
       <c r="H23" s="3">
-        <v>-146600</v>
+        <v>-149400</v>
       </c>
       <c r="I23" s="3">
-        <v>-251300</v>
+        <v>-256200</v>
       </c>
       <c r="J23" s="3">
-        <v>-7900</v>
+        <v>-8100</v>
       </c>
       <c r="K23" s="3">
         <v>86100</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>92000</v>
+        <v>93800</v>
       </c>
       <c r="E24" s="3">
         <v>-2500</v>
       </c>
       <c r="F24" s="3">
-        <v>67200</v>
+        <v>68500</v>
       </c>
       <c r="G24" s="3">
-        <v>13600</v>
+        <v>13900</v>
       </c>
       <c r="H24" s="3">
-        <v>-7400</v>
+        <v>-7600</v>
       </c>
       <c r="I24" s="3">
-        <v>-12500</v>
+        <v>-12700</v>
       </c>
       <c r="J24" s="3">
-        <v>-27200</v>
+        <v>-27800</v>
       </c>
       <c r="K24" s="3">
         <v>34400</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>260700</v>
+        <v>265700</v>
       </c>
       <c r="E26" s="3">
-        <v>-54000</v>
+        <v>-55100</v>
       </c>
       <c r="F26" s="3">
-        <v>273600</v>
+        <v>278800</v>
       </c>
       <c r="G26" s="3">
-        <v>-45400</v>
+        <v>-46300</v>
       </c>
       <c r="H26" s="3">
-        <v>-139200</v>
+        <v>-141900</v>
       </c>
       <c r="I26" s="3">
-        <v>-238800</v>
+        <v>-243400</v>
       </c>
       <c r="J26" s="3">
-        <v>19300</v>
+        <v>19700</v>
       </c>
       <c r="K26" s="3">
         <v>51700</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>257300</v>
+        <v>262300</v>
       </c>
       <c r="E27" s="3">
-        <v>-56200</v>
+        <v>-57200</v>
       </c>
       <c r="F27" s="3">
-        <v>271600</v>
+        <v>276800</v>
       </c>
       <c r="G27" s="3">
-        <v>-46900</v>
+        <v>-47800</v>
       </c>
       <c r="H27" s="3">
-        <v>-139200</v>
+        <v>-141900</v>
       </c>
       <c r="I27" s="3">
-        <v>-238800</v>
+        <v>-243400</v>
       </c>
       <c r="J27" s="3">
-        <v>19300</v>
+        <v>19700</v>
       </c>
       <c r="K27" s="3">
         <v>51700</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5300</v>
+        <v>-5400</v>
       </c>
       <c r="E32" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="F32" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G32" s="3">
-        <v>-9500</v>
+        <v>-9700</v>
       </c>
       <c r="H32" s="3">
         <v>-3300</v>
       </c>
       <c r="I32" s="3">
-        <v>-20300</v>
+        <v>-20700</v>
       </c>
       <c r="J32" s="3">
-        <v>-13100</v>
+        <v>-13400</v>
       </c>
       <c r="K32" s="3">
         <v>-14300</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>257300</v>
+        <v>262300</v>
       </c>
       <c r="E33" s="3">
-        <v>-56200</v>
+        <v>-57200</v>
       </c>
       <c r="F33" s="3">
-        <v>271600</v>
+        <v>276800</v>
       </c>
       <c r="G33" s="3">
-        <v>-46900</v>
+        <v>-47800</v>
       </c>
       <c r="H33" s="3">
-        <v>-139200</v>
+        <v>-141900</v>
       </c>
       <c r="I33" s="3">
-        <v>-238800</v>
+        <v>-243400</v>
       </c>
       <c r="J33" s="3">
-        <v>19300</v>
+        <v>19700</v>
       </c>
       <c r="K33" s="3">
         <v>51700</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>257300</v>
+        <v>262300</v>
       </c>
       <c r="E35" s="3">
-        <v>-56200</v>
+        <v>-57200</v>
       </c>
       <c r="F35" s="3">
-        <v>271600</v>
+        <v>276800</v>
       </c>
       <c r="G35" s="3">
-        <v>-46900</v>
+        <v>-47800</v>
       </c>
       <c r="H35" s="3">
-        <v>-139200</v>
+        <v>-141900</v>
       </c>
       <c r="I35" s="3">
-        <v>-238800</v>
+        <v>-243400</v>
       </c>
       <c r="J35" s="3">
-        <v>19300</v>
+        <v>19700</v>
       </c>
       <c r="K35" s="3">
         <v>51700</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>153100</v>
+        <v>156000</v>
       </c>
       <c r="E41" s="3">
-        <v>130700</v>
+        <v>133200</v>
       </c>
       <c r="F41" s="3">
-        <v>150500</v>
+        <v>153400</v>
       </c>
       <c r="G41" s="3">
-        <v>339400</v>
+        <v>345900</v>
       </c>
       <c r="H41" s="3">
-        <v>53000</v>
+        <v>54000</v>
       </c>
       <c r="I41" s="3">
-        <v>37700</v>
+        <v>38400</v>
       </c>
       <c r="J41" s="3">
-        <v>66500</v>
+        <v>67800</v>
       </c>
       <c r="K41" s="3">
         <v>68400</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>117800</v>
+        <v>120100</v>
       </c>
       <c r="E43" s="3">
-        <v>81300</v>
+        <v>82800</v>
       </c>
       <c r="F43" s="3">
-        <v>81200</v>
+        <v>82800</v>
       </c>
       <c r="G43" s="3">
-        <v>65600</v>
+        <v>66900</v>
       </c>
       <c r="H43" s="3">
-        <v>53200</v>
+        <v>54300</v>
       </c>
       <c r="I43" s="3">
-        <v>56800</v>
+        <v>57800</v>
       </c>
       <c r="J43" s="3">
-        <v>49700</v>
+        <v>50600</v>
       </c>
       <c r="K43" s="3">
         <v>34000</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>174300</v>
+        <v>177700</v>
       </c>
       <c r="E44" s="3">
-        <v>150500</v>
+        <v>153400</v>
       </c>
       <c r="F44" s="3">
-        <v>135700</v>
+        <v>138300</v>
       </c>
       <c r="G44" s="3">
-        <v>129300</v>
+        <v>131800</v>
       </c>
       <c r="H44" s="3">
-        <v>105000</v>
+        <v>107000</v>
       </c>
       <c r="I44" s="3">
-        <v>93900</v>
+        <v>95700</v>
       </c>
       <c r="J44" s="3">
-        <v>60200</v>
+        <v>61300</v>
       </c>
       <c r="K44" s="3">
         <v>63600</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>18200</v>
+        <v>18500</v>
       </c>
       <c r="E45" s="3">
-        <v>37700</v>
+        <v>38400</v>
       </c>
       <c r="F45" s="3">
-        <v>89100</v>
+        <v>90800</v>
       </c>
       <c r="G45" s="3">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="H45" s="3">
-        <v>22400</v>
+        <v>22900</v>
       </c>
       <c r="I45" s="3">
-        <v>34900</v>
+        <v>35500</v>
       </c>
       <c r="J45" s="3">
-        <v>87100</v>
+        <v>88800</v>
       </c>
       <c r="K45" s="3">
         <v>22900</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>463300</v>
+        <v>472300</v>
       </c>
       <c r="E46" s="3">
-        <v>400100</v>
+        <v>407800</v>
       </c>
       <c r="F46" s="3">
-        <v>456500</v>
+        <v>465300</v>
       </c>
       <c r="G46" s="3">
-        <v>542800</v>
+        <v>553200</v>
       </c>
       <c r="H46" s="3">
-        <v>233700</v>
+        <v>238200</v>
       </c>
       <c r="I46" s="3">
-        <v>223200</v>
+        <v>227500</v>
       </c>
       <c r="J46" s="3">
-        <v>263500</v>
+        <v>268600</v>
       </c>
       <c r="K46" s="3">
         <v>189000</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>23700</v>
+        <v>24100</v>
       </c>
       <c r="E47" s="3">
-        <v>26600</v>
+        <v>27200</v>
       </c>
       <c r="F47" s="3">
-        <v>24500</v>
+        <v>24900</v>
       </c>
       <c r="G47" s="3">
-        <v>28500</v>
+        <v>29100</v>
       </c>
       <c r="H47" s="3">
-        <v>23700</v>
+        <v>24200</v>
       </c>
       <c r="I47" s="3">
-        <v>18600</v>
+        <v>18900</v>
       </c>
       <c r="J47" s="3">
-        <v>12500</v>
+        <v>12800</v>
       </c>
       <c r="K47" s="3">
         <v>9600</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2216100</v>
+        <v>2258800</v>
       </c>
       <c r="E48" s="3">
-        <v>1755000</v>
+        <v>1788900</v>
       </c>
       <c r="F48" s="3">
-        <v>1793700</v>
+        <v>1828300</v>
       </c>
       <c r="G48" s="3">
-        <v>1558200</v>
+        <v>1588300</v>
       </c>
       <c r="H48" s="3">
-        <v>1481500</v>
+        <v>1510100</v>
       </c>
       <c r="I48" s="3">
-        <v>1655100</v>
+        <v>1687100</v>
       </c>
       <c r="J48" s="3">
-        <v>1604000</v>
+        <v>1635000</v>
       </c>
       <c r="K48" s="3">
         <v>1630000</v>
@@ -2359,19 +2359,19 @@
         <v>2600</v>
       </c>
       <c r="F49" s="3">
-        <v>19500</v>
+        <v>19900</v>
       </c>
       <c r="G49" s="3">
-        <v>28600</v>
+        <v>29200</v>
       </c>
       <c r="H49" s="3">
-        <v>28500</v>
+        <v>29000</v>
       </c>
       <c r="I49" s="3">
-        <v>27500</v>
+        <v>28000</v>
       </c>
       <c r="J49" s="3">
-        <v>32200</v>
+        <v>32800</v>
       </c>
       <c r="K49" s="3">
         <v>47400</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>351300</v>
+        <v>358000</v>
       </c>
       <c r="E52" s="3">
-        <v>314700</v>
+        <v>320800</v>
       </c>
       <c r="F52" s="3">
-        <v>311400</v>
+        <v>317400</v>
       </c>
       <c r="G52" s="3">
-        <v>228000</v>
+        <v>232400</v>
       </c>
       <c r="H52" s="3">
-        <v>194000</v>
+        <v>197700</v>
       </c>
       <c r="I52" s="3">
-        <v>185700</v>
+        <v>189300</v>
       </c>
       <c r="J52" s="3">
-        <v>163700</v>
+        <v>166900</v>
       </c>
       <c r="K52" s="3">
         <v>141400</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3056000</v>
+        <v>3115000</v>
       </c>
       <c r="E54" s="3">
-        <v>2499100</v>
+        <v>2547300</v>
       </c>
       <c r="F54" s="3">
-        <v>2605600</v>
+        <v>2655900</v>
       </c>
       <c r="G54" s="3">
-        <v>2386100</v>
+        <v>2432100</v>
       </c>
       <c r="H54" s="3">
-        <v>1961300</v>
+        <v>1999200</v>
       </c>
       <c r="I54" s="3">
-        <v>2110100</v>
+        <v>2150800</v>
       </c>
       <c r="J54" s="3">
-        <v>2076000</v>
+        <v>2116000</v>
       </c>
       <c r="K54" s="3">
         <v>2017400</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>64300</v>
+        <v>65600</v>
       </c>
       <c r="E57" s="3">
-        <v>67600</v>
+        <v>68900</v>
       </c>
       <c r="F57" s="3">
-        <v>67800</v>
+        <v>69100</v>
       </c>
       <c r="G57" s="3">
-        <v>37700</v>
+        <v>38400</v>
       </c>
       <c r="H57" s="3">
-        <v>40700</v>
+        <v>41500</v>
       </c>
       <c r="I57" s="3">
-        <v>31300</v>
+        <v>31900</v>
       </c>
       <c r="J57" s="3">
-        <v>27800</v>
+        <v>28400</v>
       </c>
       <c r="K57" s="3">
         <v>19200</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>17000</v>
+        <v>17400</v>
       </c>
       <c r="E58" s="3">
-        <v>11900</v>
+        <v>12100</v>
       </c>
       <c r="F58" s="3">
-        <v>26400</v>
+        <v>26900</v>
       </c>
       <c r="G58" s="3">
-        <v>16800</v>
+        <v>17100</v>
       </c>
       <c r="H58" s="3">
         <v>4800</v>
       </c>
       <c r="I58" s="3">
-        <v>36800</v>
+        <v>37500</v>
       </c>
       <c r="J58" s="3">
-        <v>97900</v>
+        <v>99800</v>
       </c>
       <c r="K58" s="3">
         <v>16300</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>285300</v>
+        <v>290800</v>
       </c>
       <c r="E59" s="3">
-        <v>186200</v>
+        <v>189800</v>
       </c>
       <c r="F59" s="3">
-        <v>202300</v>
+        <v>206300</v>
       </c>
       <c r="G59" s="3">
-        <v>349100</v>
+        <v>355900</v>
       </c>
       <c r="H59" s="3">
-        <v>127200</v>
+        <v>129600</v>
       </c>
       <c r="I59" s="3">
-        <v>124000</v>
+        <v>126400</v>
       </c>
       <c r="J59" s="3">
-        <v>79500</v>
+        <v>81000</v>
       </c>
       <c r="K59" s="3">
         <v>75100</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>366600</v>
+        <v>373700</v>
       </c>
       <c r="E60" s="3">
-        <v>265600</v>
+        <v>270700</v>
       </c>
       <c r="F60" s="3">
-        <v>296500</v>
+        <v>302200</v>
       </c>
       <c r="G60" s="3">
-        <v>403600</v>
+        <v>411400</v>
       </c>
       <c r="H60" s="3">
-        <v>172700</v>
+        <v>176000</v>
       </c>
       <c r="I60" s="3">
-        <v>192200</v>
+        <v>195900</v>
       </c>
       <c r="J60" s="3">
-        <v>205200</v>
+        <v>209200</v>
       </c>
       <c r="K60" s="3">
         <v>110600</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>315100</v>
+        <v>321200</v>
       </c>
       <c r="E61" s="3">
-        <v>182900</v>
+        <v>186400</v>
       </c>
       <c r="F61" s="3">
-        <v>167000</v>
+        <v>170200</v>
       </c>
       <c r="G61" s="3">
-        <v>402800</v>
+        <v>410500</v>
       </c>
       <c r="H61" s="3">
-        <v>311100</v>
+        <v>317100</v>
       </c>
       <c r="I61" s="3">
-        <v>262900</v>
+        <v>268000</v>
       </c>
       <c r="J61" s="3">
-        <v>16000</v>
+        <v>16300</v>
       </c>
       <c r="K61" s="3">
         <v>111100</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>512100</v>
+        <v>521900</v>
       </c>
       <c r="E62" s="3">
-        <v>442700</v>
+        <v>451200</v>
       </c>
       <c r="F62" s="3">
-        <v>475600</v>
+        <v>484800</v>
       </c>
       <c r="G62" s="3">
-        <v>331700</v>
+        <v>338100</v>
       </c>
       <c r="H62" s="3">
-        <v>270300</v>
+        <v>275500</v>
       </c>
       <c r="I62" s="3">
-        <v>299900</v>
+        <v>305700</v>
       </c>
       <c r="J62" s="3">
-        <v>290900</v>
+        <v>296500</v>
       </c>
       <c r="K62" s="3">
         <v>260500</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1200400</v>
+        <v>1223500</v>
       </c>
       <c r="E66" s="3">
-        <v>895300</v>
+        <v>912600</v>
       </c>
       <c r="F66" s="3">
-        <v>942000</v>
+        <v>960100</v>
       </c>
       <c r="G66" s="3">
-        <v>1138300</v>
+        <v>1160300</v>
       </c>
       <c r="H66" s="3">
-        <v>754000</v>
+        <v>768500</v>
       </c>
       <c r="I66" s="3">
-        <v>755000</v>
+        <v>769600</v>
       </c>
       <c r="J66" s="3">
-        <v>512100</v>
+        <v>522000</v>
       </c>
       <c r="K66" s="3">
         <v>482200</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-110600</v>
+        <v>-112700</v>
       </c>
       <c r="E72" s="3">
-        <v>-366700</v>
+        <v>-373800</v>
       </c>
       <c r="F72" s="3">
-        <v>-296100</v>
+        <v>-301800</v>
       </c>
       <c r="G72" s="3">
-        <v>-539900</v>
+        <v>-550300</v>
       </c>
       <c r="H72" s="3">
-        <v>-503200</v>
+        <v>-512900</v>
       </c>
       <c r="I72" s="3">
-        <v>-376300</v>
+        <v>-383600</v>
       </c>
       <c r="J72" s="3">
-        <v>-149800</v>
+        <v>-152600</v>
       </c>
       <c r="K72" s="3">
         <v>-168800</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1855700</v>
+        <v>1891500</v>
       </c>
       <c r="E76" s="3">
-        <v>1603800</v>
+        <v>1634700</v>
       </c>
       <c r="F76" s="3">
-        <v>1663600</v>
+        <v>1695700</v>
       </c>
       <c r="G76" s="3">
-        <v>1247800</v>
+        <v>1271800</v>
       </c>
       <c r="H76" s="3">
-        <v>1207400</v>
+        <v>1230700</v>
       </c>
       <c r="I76" s="3">
-        <v>1355100</v>
+        <v>1381300</v>
       </c>
       <c r="J76" s="3">
-        <v>1563800</v>
+        <v>1594000</v>
       </c>
       <c r="K76" s="3">
         <v>1535200</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>257300</v>
+        <v>262300</v>
       </c>
       <c r="E81" s="3">
-        <v>-56200</v>
+        <v>-57200</v>
       </c>
       <c r="F81" s="3">
-        <v>271600</v>
+        <v>276800</v>
       </c>
       <c r="G81" s="3">
-        <v>-46900</v>
+        <v>-47800</v>
       </c>
       <c r="H81" s="3">
-        <v>-139200</v>
+        <v>-141900</v>
       </c>
       <c r="I81" s="3">
-        <v>-238800</v>
+        <v>-243400</v>
       </c>
       <c r="J81" s="3">
-        <v>19300</v>
+        <v>19700</v>
       </c>
       <c r="K81" s="3">
         <v>51700</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>184400</v>
+        <v>188000</v>
       </c>
       <c r="E83" s="3">
-        <v>196600</v>
+        <v>200400</v>
       </c>
       <c r="F83" s="3">
-        <v>207000</v>
+        <v>211000</v>
       </c>
       <c r="G83" s="3">
-        <v>187300</v>
+        <v>190900</v>
       </c>
       <c r="H83" s="3">
-        <v>216400</v>
+        <v>220600</v>
       </c>
       <c r="I83" s="3">
-        <v>137200</v>
+        <v>139900</v>
       </c>
       <c r="J83" s="3">
-        <v>134500</v>
+        <v>137100</v>
       </c>
       <c r="K83" s="3">
         <v>118200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>531100</v>
+        <v>541400</v>
       </c>
       <c r="E89" s="3">
-        <v>369700</v>
+        <v>376800</v>
       </c>
       <c r="F89" s="3">
-        <v>490100</v>
+        <v>499500</v>
       </c>
       <c r="G89" s="3">
-        <v>252200</v>
+        <v>257000</v>
       </c>
       <c r="H89" s="3">
-        <v>249800</v>
+        <v>254600</v>
       </c>
       <c r="I89" s="3">
-        <v>207400</v>
+        <v>211400</v>
       </c>
       <c r="J89" s="3">
-        <v>203100</v>
+        <v>207000</v>
       </c>
       <c r="K89" s="3">
         <v>245900</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-407900</v>
+        <v>-415800</v>
       </c>
       <c r="E91" s="3">
-        <v>-331800</v>
+        <v>-338200</v>
       </c>
       <c r="F91" s="3">
-        <v>-274500</v>
+        <v>-279800</v>
       </c>
       <c r="G91" s="3">
-        <v>-192300</v>
+        <v>-196000</v>
       </c>
       <c r="H91" s="3">
-        <v>-268800</v>
+        <v>-274000</v>
       </c>
       <c r="I91" s="3">
-        <v>-243600</v>
+        <v>-248300</v>
       </c>
       <c r="J91" s="3">
-        <v>-207700</v>
+        <v>-211700</v>
       </c>
       <c r="K91" s="3">
         <v>-132800</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-565700</v>
+        <v>-576600</v>
       </c>
       <c r="E94" s="3">
-        <v>-331000</v>
+        <v>-337400</v>
       </c>
       <c r="F94" s="3">
-        <v>-451900</v>
+        <v>-460600</v>
       </c>
       <c r="G94" s="3">
-        <v>-190000</v>
+        <v>-193600</v>
       </c>
       <c r="H94" s="3">
-        <v>-256100</v>
+        <v>-261100</v>
       </c>
       <c r="I94" s="3">
-        <v>-431100</v>
+        <v>-439400</v>
       </c>
       <c r="J94" s="3">
-        <v>-180600</v>
+        <v>-184100</v>
       </c>
       <c r="K94" s="3">
         <v>-141600</v>
@@ -4227,13 +4227,13 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-8200</v>
+        <v>-8400</v>
       </c>
       <c r="E96" s="3">
-        <v>-23000</v>
+        <v>-23400</v>
       </c>
       <c r="F96" s="3">
-        <v>-36500</v>
+        <v>-37200</v>
       </c>
       <c r="G96" s="3">
         <v>-200</v>
@@ -4242,10 +4242,10 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-8200</v>
+        <v>-8400</v>
       </c>
       <c r="J96" s="3">
-        <v>-23400</v>
+        <v>-23900</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>63700</v>
+        <v>65000</v>
       </c>
       <c r="E100" s="3">
-        <v>-61500</v>
+        <v>-62600</v>
       </c>
       <c r="F100" s="3">
-        <v>-229500</v>
+        <v>-234000</v>
       </c>
       <c r="G100" s="3">
-        <v>229800</v>
+        <v>234300</v>
       </c>
       <c r="H100" s="3">
-        <v>20300</v>
+        <v>20700</v>
       </c>
       <c r="I100" s="3">
-        <v>198800</v>
+        <v>202600</v>
       </c>
       <c r="J100" s="3">
-        <v>-24000</v>
+        <v>-24500</v>
       </c>
       <c r="K100" s="3">
         <v>-95100</v>
@@ -4452,7 +4452,7 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-6800</v>
+        <v>-6900</v>
       </c>
       <c r="E101" s="3">
         <v>3000</v>
@@ -4461,13 +4461,13 @@
         <v>2500</v>
       </c>
       <c r="G101" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="H101" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="I101" s="3">
-        <v>-3800</v>
+        <v>-3900</v>
       </c>
       <c r="J101" s="3">
         <v>1000</v>
@@ -4497,22 +4497,22 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>22400</v>
+        <v>22800</v>
       </c>
       <c r="E102" s="3">
-        <v>-19800</v>
+        <v>-20200</v>
       </c>
       <c r="F102" s="3">
-        <v>-188900</v>
+        <v>-192500</v>
       </c>
       <c r="G102" s="3">
-        <v>286400</v>
+        <v>291900</v>
       </c>
       <c r="H102" s="3">
-        <v>15300</v>
+        <v>15600</v>
       </c>
       <c r="I102" s="3">
-        <v>-28800</v>
+        <v>-29400</v>
       </c>
       <c r="J102" s="3">
         <v>-500</v>

--- a/AAII_Financials/Yearly/HMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HMY_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2681500</v>
+        <v>2776600</v>
       </c>
       <c r="E8" s="3">
-        <v>2320700</v>
+        <v>2403000</v>
       </c>
       <c r="F8" s="3">
-        <v>2271100</v>
+        <v>2351700</v>
       </c>
       <c r="G8" s="3">
-        <v>1591500</v>
+        <v>1648000</v>
       </c>
       <c r="H8" s="3">
-        <v>1464600</v>
+        <v>1516500</v>
       </c>
       <c r="I8" s="3">
-        <v>1113000</v>
+        <v>1152500</v>
       </c>
       <c r="J8" s="3">
-        <v>1048300</v>
+        <v>1085500</v>
       </c>
       <c r="K8" s="3">
         <v>998800</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2149900</v>
+        <v>2226100</v>
       </c>
       <c r="E9" s="3">
-        <v>2038700</v>
+        <v>2111000</v>
       </c>
       <c r="F9" s="3">
-        <v>1852100</v>
+        <v>1917800</v>
       </c>
       <c r="G9" s="3">
-        <v>1407700</v>
+        <v>1457700</v>
       </c>
       <c r="H9" s="3">
-        <v>1345800</v>
+        <v>1393500</v>
       </c>
       <c r="I9" s="3">
-        <v>982400</v>
+        <v>1017200</v>
       </c>
       <c r="J9" s="3">
-        <v>971200</v>
+        <v>1005700</v>
       </c>
       <c r="K9" s="3">
         <v>861500</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>531700</v>
+        <v>550500</v>
       </c>
       <c r="E10" s="3">
-        <v>282000</v>
+        <v>292000</v>
       </c>
       <c r="F10" s="3">
-        <v>419000</v>
+        <v>433900</v>
       </c>
       <c r="G10" s="3">
-        <v>183800</v>
+        <v>190300</v>
       </c>
       <c r="H10" s="3">
-        <v>118800</v>
+        <v>123000</v>
       </c>
       <c r="I10" s="3">
-        <v>130600</v>
+        <v>135200</v>
       </c>
       <c r="J10" s="3">
-        <v>77100</v>
+        <v>79800</v>
       </c>
       <c r="K10" s="3">
         <v>137300</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>27500</v>
+        <v>28500</v>
       </c>
       <c r="E12" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F12" s="3">
+        <v>10000</v>
+      </c>
+      <c r="G12" s="3">
         <v>11600</v>
       </c>
-      <c r="F12" s="3">
-        <v>9600</v>
-      </c>
-      <c r="G12" s="3">
-        <v>11200</v>
-      </c>
       <c r="H12" s="3">
-        <v>8100</v>
+        <v>8300</v>
       </c>
       <c r="I12" s="3">
-        <v>7300</v>
+        <v>7600</v>
       </c>
       <c r="J12" s="3">
-        <v>13100</v>
+        <v>13600</v>
       </c>
       <c r="K12" s="3">
         <v>10400</v>
@@ -970,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="E14" s="3">
-        <v>244200</v>
+        <v>252800</v>
       </c>
       <c r="F14" s="3">
-        <v>73800</v>
+        <v>76500</v>
       </c>
       <c r="G14" s="3">
-        <v>6600</v>
+        <v>6800</v>
       </c>
       <c r="H14" s="3">
-        <v>221900</v>
+        <v>229800</v>
       </c>
       <c r="I14" s="3">
-        <v>301000</v>
+        <v>311700</v>
       </c>
       <c r="J14" s="3">
-        <v>102000</v>
+        <v>105700</v>
       </c>
       <c r="K14" s="3">
         <v>-1500</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2307100</v>
+        <v>2389000</v>
       </c>
       <c r="E17" s="3">
-        <v>2361800</v>
+        <v>2445600</v>
       </c>
       <c r="F17" s="3">
-        <v>1910400</v>
+        <v>1978100</v>
       </c>
       <c r="G17" s="3">
-        <v>1613400</v>
+        <v>1670700</v>
       </c>
       <c r="H17" s="3">
-        <v>1602700</v>
+        <v>1659500</v>
       </c>
       <c r="I17" s="3">
-        <v>1371900</v>
+        <v>1420600</v>
       </c>
       <c r="J17" s="3">
-        <v>1057100</v>
+        <v>1094500</v>
       </c>
       <c r="K17" s="3">
         <v>912100</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>374400</v>
+        <v>387700</v>
       </c>
       <c r="E18" s="3">
-        <v>-41100</v>
+        <v>-42500</v>
       </c>
       <c r="F18" s="3">
-        <v>360800</v>
+        <v>373500</v>
       </c>
       <c r="G18" s="3">
-        <v>-21900</v>
+        <v>-22700</v>
       </c>
       <c r="H18" s="3">
-        <v>-138100</v>
+        <v>-143000</v>
       </c>
       <c r="I18" s="3">
-        <v>-258900</v>
+        <v>-268100</v>
       </c>
       <c r="J18" s="3">
-        <v>-8700</v>
+        <v>-9000</v>
       </c>
       <c r="K18" s="3">
         <v>86700</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>5400</v>
+        <v>5600</v>
       </c>
       <c r="E20" s="3">
-        <v>-5900</v>
+        <v>-6100</v>
       </c>
       <c r="F20" s="3">
         <v>-1500</v>
       </c>
       <c r="G20" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="H20" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="I20" s="3">
-        <v>20700</v>
+        <v>21500</v>
       </c>
       <c r="J20" s="3">
-        <v>13400</v>
+        <v>13900</v>
       </c>
       <c r="K20" s="3">
         <v>14300</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>565500</v>
+        <v>587700</v>
       </c>
       <c r="E21" s="3">
-        <v>151100</v>
+        <v>158600</v>
       </c>
       <c r="F21" s="3">
-        <v>567700</v>
+        <v>590200</v>
       </c>
       <c r="G21" s="3">
-        <v>176400</v>
+        <v>184800</v>
       </c>
       <c r="H21" s="3">
-        <v>83200</v>
+        <v>88600</v>
       </c>
       <c r="I21" s="3">
-        <v>-100000</v>
+        <v>-102000</v>
       </c>
       <c r="J21" s="3">
-        <v>140100</v>
+        <v>146600</v>
       </c>
       <c r="K21" s="3">
         <v>220500</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>20300</v>
+        <v>21000</v>
       </c>
       <c r="E22" s="3">
-        <v>10600</v>
+        <v>11000</v>
       </c>
       <c r="F22" s="3">
-        <v>12000</v>
+        <v>12400</v>
       </c>
       <c r="G22" s="3">
-        <v>20100</v>
+        <v>20800</v>
       </c>
       <c r="H22" s="3">
-        <v>14600</v>
+        <v>15200</v>
       </c>
       <c r="I22" s="3">
-        <v>18000</v>
+        <v>18600</v>
       </c>
       <c r="J22" s="3">
-        <v>12700</v>
+        <v>13200</v>
       </c>
       <c r="K22" s="3">
         <v>14900</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>359500</v>
+        <v>372200</v>
       </c>
       <c r="E23" s="3">
-        <v>-57600</v>
+        <v>-59600</v>
       </c>
       <c r="F23" s="3">
-        <v>347300</v>
+        <v>359600</v>
       </c>
       <c r="G23" s="3">
-        <v>-32400</v>
+        <v>-33500</v>
       </c>
       <c r="H23" s="3">
-        <v>-149400</v>
+        <v>-154700</v>
       </c>
       <c r="I23" s="3">
-        <v>-256200</v>
+        <v>-265200</v>
       </c>
       <c r="J23" s="3">
-        <v>-8100</v>
+        <v>-8300</v>
       </c>
       <c r="K23" s="3">
         <v>86100</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>93800</v>
+        <v>97100</v>
       </c>
       <c r="E24" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="F24" s="3">
-        <v>68500</v>
+        <v>70900</v>
       </c>
       <c r="G24" s="3">
-        <v>13900</v>
+        <v>14400</v>
       </c>
       <c r="H24" s="3">
-        <v>-7600</v>
+        <v>-7800</v>
       </c>
       <c r="I24" s="3">
-        <v>-12700</v>
+        <v>-13200</v>
       </c>
       <c r="J24" s="3">
-        <v>-27800</v>
+        <v>-28700</v>
       </c>
       <c r="K24" s="3">
         <v>34400</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>265700</v>
+        <v>275200</v>
       </c>
       <c r="E26" s="3">
-        <v>-55100</v>
+        <v>-57000</v>
       </c>
       <c r="F26" s="3">
-        <v>278800</v>
+        <v>288700</v>
       </c>
       <c r="G26" s="3">
-        <v>-46300</v>
+        <v>-47900</v>
       </c>
       <c r="H26" s="3">
-        <v>-141900</v>
+        <v>-146900</v>
       </c>
       <c r="I26" s="3">
-        <v>-243400</v>
+        <v>-252100</v>
       </c>
       <c r="J26" s="3">
-        <v>19700</v>
+        <v>20400</v>
       </c>
       <c r="K26" s="3">
         <v>51700</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>262300</v>
+        <v>271600</v>
       </c>
       <c r="E27" s="3">
-        <v>-57200</v>
+        <v>-59300</v>
       </c>
       <c r="F27" s="3">
-        <v>276800</v>
+        <v>286700</v>
       </c>
       <c r="G27" s="3">
-        <v>-47800</v>
+        <v>-49500</v>
       </c>
       <c r="H27" s="3">
-        <v>-141900</v>
+        <v>-146900</v>
       </c>
       <c r="I27" s="3">
-        <v>-243400</v>
+        <v>-252100</v>
       </c>
       <c r="J27" s="3">
-        <v>19700</v>
+        <v>20400</v>
       </c>
       <c r="K27" s="3">
         <v>51700</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5400</v>
+        <v>-5600</v>
       </c>
       <c r="E32" s="3">
-        <v>5900</v>
+        <v>6100</v>
       </c>
       <c r="F32" s="3">
         <v>1500</v>
       </c>
       <c r="G32" s="3">
-        <v>-9700</v>
+        <v>-10000</v>
       </c>
       <c r="H32" s="3">
-        <v>-3300</v>
+        <v>-3400</v>
       </c>
       <c r="I32" s="3">
-        <v>-20700</v>
+        <v>-21500</v>
       </c>
       <c r="J32" s="3">
-        <v>-13400</v>
+        <v>-13900</v>
       </c>
       <c r="K32" s="3">
         <v>-14300</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>262300</v>
+        <v>271600</v>
       </c>
       <c r="E33" s="3">
-        <v>-57200</v>
+        <v>-59300</v>
       </c>
       <c r="F33" s="3">
-        <v>276800</v>
+        <v>286700</v>
       </c>
       <c r="G33" s="3">
-        <v>-47800</v>
+        <v>-49500</v>
       </c>
       <c r="H33" s="3">
-        <v>-141900</v>
+        <v>-146900</v>
       </c>
       <c r="I33" s="3">
-        <v>-243400</v>
+        <v>-252100</v>
       </c>
       <c r="J33" s="3">
-        <v>19700</v>
+        <v>20400</v>
       </c>
       <c r="K33" s="3">
         <v>51700</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>262300</v>
+        <v>271600</v>
       </c>
       <c r="E35" s="3">
-        <v>-57200</v>
+        <v>-59300</v>
       </c>
       <c r="F35" s="3">
-        <v>276800</v>
+        <v>286700</v>
       </c>
       <c r="G35" s="3">
-        <v>-47800</v>
+        <v>-49500</v>
       </c>
       <c r="H35" s="3">
-        <v>-141900</v>
+        <v>-146900</v>
       </c>
       <c r="I35" s="3">
-        <v>-243400</v>
+        <v>-252100</v>
       </c>
       <c r="J35" s="3">
-        <v>19700</v>
+        <v>20400</v>
       </c>
       <c r="K35" s="3">
         <v>51700</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>156000</v>
+        <v>161600</v>
       </c>
       <c r="E41" s="3">
-        <v>133200</v>
+        <v>137900</v>
       </c>
       <c r="F41" s="3">
-        <v>153400</v>
+        <v>158900</v>
       </c>
       <c r="G41" s="3">
-        <v>345900</v>
+        <v>358200</v>
       </c>
       <c r="H41" s="3">
-        <v>54000</v>
+        <v>56000</v>
       </c>
       <c r="I41" s="3">
-        <v>38400</v>
+        <v>39800</v>
       </c>
       <c r="J41" s="3">
-        <v>67800</v>
+        <v>70200</v>
       </c>
       <c r="K41" s="3">
         <v>68400</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>120100</v>
+        <v>124300</v>
       </c>
       <c r="E43" s="3">
-        <v>82800</v>
+        <v>85800</v>
       </c>
       <c r="F43" s="3">
-        <v>82800</v>
+        <v>85700</v>
       </c>
       <c r="G43" s="3">
-        <v>66900</v>
+        <v>69300</v>
       </c>
       <c r="H43" s="3">
-        <v>54300</v>
+        <v>56200</v>
       </c>
       <c r="I43" s="3">
-        <v>57800</v>
+        <v>59900</v>
       </c>
       <c r="J43" s="3">
-        <v>50600</v>
+        <v>52400</v>
       </c>
       <c r="K43" s="3">
         <v>34000</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>177700</v>
+        <v>184000</v>
       </c>
       <c r="E44" s="3">
-        <v>153400</v>
+        <v>158800</v>
       </c>
       <c r="F44" s="3">
-        <v>138300</v>
+        <v>143200</v>
       </c>
       <c r="G44" s="3">
-        <v>131800</v>
+        <v>136400</v>
       </c>
       <c r="H44" s="3">
-        <v>107000</v>
+        <v>110800</v>
       </c>
       <c r="I44" s="3">
-        <v>95700</v>
+        <v>99100</v>
       </c>
       <c r="J44" s="3">
-        <v>61300</v>
+        <v>63500</v>
       </c>
       <c r="K44" s="3">
         <v>63600</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>18500</v>
+        <v>19200</v>
       </c>
       <c r="E45" s="3">
-        <v>38400</v>
+        <v>39800</v>
       </c>
       <c r="F45" s="3">
-        <v>90800</v>
+        <v>94000</v>
       </c>
       <c r="G45" s="3">
-        <v>8700</v>
+        <v>9000</v>
       </c>
       <c r="H45" s="3">
-        <v>22900</v>
+        <v>23700</v>
       </c>
       <c r="I45" s="3">
-        <v>35500</v>
+        <v>36800</v>
       </c>
       <c r="J45" s="3">
-        <v>88800</v>
+        <v>92000</v>
       </c>
       <c r="K45" s="3">
         <v>22900</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>472300</v>
+        <v>489000</v>
       </c>
       <c r="E46" s="3">
-        <v>407800</v>
+        <v>422300</v>
       </c>
       <c r="F46" s="3">
-        <v>465300</v>
+        <v>481800</v>
       </c>
       <c r="G46" s="3">
-        <v>553200</v>
+        <v>572900</v>
       </c>
       <c r="H46" s="3">
-        <v>238200</v>
+        <v>246600</v>
       </c>
       <c r="I46" s="3">
-        <v>227500</v>
+        <v>235600</v>
       </c>
       <c r="J46" s="3">
-        <v>268600</v>
+        <v>278100</v>
       </c>
       <c r="K46" s="3">
         <v>189000</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>24100</v>
+        <v>25000</v>
       </c>
       <c r="E47" s="3">
-        <v>27200</v>
+        <v>28100</v>
       </c>
       <c r="F47" s="3">
-        <v>24900</v>
+        <v>25800</v>
       </c>
       <c r="G47" s="3">
-        <v>29100</v>
+        <v>30100</v>
       </c>
       <c r="H47" s="3">
-        <v>24200</v>
+        <v>25000</v>
       </c>
       <c r="I47" s="3">
-        <v>18900</v>
+        <v>19600</v>
       </c>
       <c r="J47" s="3">
-        <v>12800</v>
+        <v>13200</v>
       </c>
       <c r="K47" s="3">
         <v>9600</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2258800</v>
+        <v>2338900</v>
       </c>
       <c r="E48" s="3">
-        <v>1788900</v>
+        <v>1852300</v>
       </c>
       <c r="F48" s="3">
-        <v>1828300</v>
+        <v>1893200</v>
       </c>
       <c r="G48" s="3">
-        <v>1588300</v>
+        <v>1644600</v>
       </c>
       <c r="H48" s="3">
-        <v>1510100</v>
+        <v>1563700</v>
       </c>
       <c r="I48" s="3">
-        <v>1687100</v>
+        <v>1746900</v>
       </c>
       <c r="J48" s="3">
-        <v>1635000</v>
+        <v>1693000</v>
       </c>
       <c r="K48" s="3">
         <v>1630000</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="E49" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="F49" s="3">
-        <v>19900</v>
+        <v>20600</v>
       </c>
       <c r="G49" s="3">
-        <v>29200</v>
+        <v>30200</v>
       </c>
       <c r="H49" s="3">
+        <v>30000</v>
+      </c>
+      <c r="I49" s="3">
         <v>29000</v>
       </c>
-      <c r="I49" s="3">
-        <v>28000</v>
-      </c>
       <c r="J49" s="3">
-        <v>32800</v>
+        <v>34000</v>
       </c>
       <c r="K49" s="3">
         <v>47400</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>358000</v>
+        <v>370700</v>
       </c>
       <c r="E52" s="3">
-        <v>320800</v>
+        <v>332200</v>
       </c>
       <c r="F52" s="3">
-        <v>317400</v>
+        <v>328600</v>
       </c>
       <c r="G52" s="3">
-        <v>232400</v>
+        <v>240600</v>
       </c>
       <c r="H52" s="3">
-        <v>197700</v>
+        <v>204700</v>
       </c>
       <c r="I52" s="3">
-        <v>189300</v>
+        <v>196000</v>
       </c>
       <c r="J52" s="3">
-        <v>166900</v>
+        <v>172800</v>
       </c>
       <c r="K52" s="3">
         <v>141400</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3115000</v>
+        <v>3225500</v>
       </c>
       <c r="E54" s="3">
-        <v>2547300</v>
+        <v>2637600</v>
       </c>
       <c r="F54" s="3">
-        <v>2655900</v>
+        <v>2750000</v>
       </c>
       <c r="G54" s="3">
-        <v>2432100</v>
+        <v>2518400</v>
       </c>
       <c r="H54" s="3">
-        <v>1999200</v>
+        <v>2070100</v>
       </c>
       <c r="I54" s="3">
-        <v>2150800</v>
+        <v>2227100</v>
       </c>
       <c r="J54" s="3">
-        <v>2116000</v>
+        <v>2191100</v>
       </c>
       <c r="K54" s="3">
         <v>2017400</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>65600</v>
+        <v>67900</v>
       </c>
       <c r="E57" s="3">
-        <v>68900</v>
+        <v>71300</v>
       </c>
       <c r="F57" s="3">
-        <v>69100</v>
+        <v>71500</v>
       </c>
       <c r="G57" s="3">
-        <v>38400</v>
+        <v>39800</v>
       </c>
       <c r="H57" s="3">
-        <v>41500</v>
+        <v>43000</v>
       </c>
       <c r="I57" s="3">
-        <v>31900</v>
+        <v>33100</v>
       </c>
       <c r="J57" s="3">
-        <v>28400</v>
+        <v>29400</v>
       </c>
       <c r="K57" s="3">
         <v>19200</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>17400</v>
+        <v>18000</v>
       </c>
       <c r="E58" s="3">
-        <v>12100</v>
+        <v>12500</v>
       </c>
       <c r="F58" s="3">
-        <v>26900</v>
+        <v>27800</v>
       </c>
       <c r="G58" s="3">
-        <v>17100</v>
+        <v>17800</v>
       </c>
       <c r="H58" s="3">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="I58" s="3">
-        <v>37500</v>
+        <v>38900</v>
       </c>
       <c r="J58" s="3">
-        <v>99800</v>
+        <v>103300</v>
       </c>
       <c r="K58" s="3">
         <v>16300</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>290800</v>
+        <v>301100</v>
       </c>
       <c r="E59" s="3">
-        <v>189800</v>
+        <v>196500</v>
       </c>
       <c r="F59" s="3">
-        <v>206300</v>
+        <v>213600</v>
       </c>
       <c r="G59" s="3">
-        <v>355900</v>
+        <v>368500</v>
       </c>
       <c r="H59" s="3">
-        <v>129600</v>
+        <v>134200</v>
       </c>
       <c r="I59" s="3">
-        <v>126400</v>
+        <v>130800</v>
       </c>
       <c r="J59" s="3">
-        <v>81000</v>
+        <v>83900</v>
       </c>
       <c r="K59" s="3">
         <v>75100</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>373700</v>
+        <v>387000</v>
       </c>
       <c r="E60" s="3">
-        <v>270700</v>
+        <v>280300</v>
       </c>
       <c r="F60" s="3">
-        <v>302200</v>
+        <v>312900</v>
       </c>
       <c r="G60" s="3">
-        <v>411400</v>
+        <v>426000</v>
       </c>
       <c r="H60" s="3">
-        <v>176000</v>
+        <v>182200</v>
       </c>
       <c r="I60" s="3">
-        <v>195900</v>
+        <v>202800</v>
       </c>
       <c r="J60" s="3">
-        <v>209200</v>
+        <v>216600</v>
       </c>
       <c r="K60" s="3">
         <v>110600</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>321200</v>
+        <v>332600</v>
       </c>
       <c r="E61" s="3">
-        <v>186400</v>
+        <v>193000</v>
       </c>
       <c r="F61" s="3">
-        <v>170200</v>
+        <v>176300</v>
       </c>
       <c r="G61" s="3">
-        <v>410500</v>
+        <v>425100</v>
       </c>
       <c r="H61" s="3">
-        <v>317100</v>
+        <v>328300</v>
       </c>
       <c r="I61" s="3">
-        <v>268000</v>
+        <v>277500</v>
       </c>
       <c r="J61" s="3">
-        <v>16300</v>
+        <v>16800</v>
       </c>
       <c r="K61" s="3">
         <v>111100</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>521900</v>
+        <v>540500</v>
       </c>
       <c r="E62" s="3">
-        <v>451200</v>
+        <v>467200</v>
       </c>
       <c r="F62" s="3">
-        <v>484800</v>
+        <v>502000</v>
       </c>
       <c r="G62" s="3">
-        <v>338100</v>
+        <v>350100</v>
       </c>
       <c r="H62" s="3">
-        <v>275500</v>
+        <v>285200</v>
       </c>
       <c r="I62" s="3">
-        <v>305700</v>
+        <v>316600</v>
       </c>
       <c r="J62" s="3">
-        <v>296500</v>
+        <v>307100</v>
       </c>
       <c r="K62" s="3">
         <v>260500</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1223500</v>
+        <v>1266900</v>
       </c>
       <c r="E66" s="3">
-        <v>912600</v>
+        <v>944900</v>
       </c>
       <c r="F66" s="3">
-        <v>960100</v>
+        <v>994200</v>
       </c>
       <c r="G66" s="3">
-        <v>1160300</v>
+        <v>1201400</v>
       </c>
       <c r="H66" s="3">
-        <v>768500</v>
+        <v>795800</v>
       </c>
       <c r="I66" s="3">
-        <v>769600</v>
+        <v>796800</v>
       </c>
       <c r="J66" s="3">
-        <v>522000</v>
+        <v>540500</v>
       </c>
       <c r="K66" s="3">
         <v>482200</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-112700</v>
+        <v>-116700</v>
       </c>
       <c r="E72" s="3">
-        <v>-373800</v>
+        <v>-387100</v>
       </c>
       <c r="F72" s="3">
-        <v>-301800</v>
+        <v>-312500</v>
       </c>
       <c r="G72" s="3">
-        <v>-550300</v>
+        <v>-569800</v>
       </c>
       <c r="H72" s="3">
-        <v>-512900</v>
+        <v>-531100</v>
       </c>
       <c r="I72" s="3">
-        <v>-383600</v>
+        <v>-397200</v>
       </c>
       <c r="J72" s="3">
-        <v>-152600</v>
+        <v>-158100</v>
       </c>
       <c r="K72" s="3">
         <v>-168800</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1891500</v>
+        <v>1958600</v>
       </c>
       <c r="E76" s="3">
-        <v>1634700</v>
+        <v>1692700</v>
       </c>
       <c r="F76" s="3">
-        <v>1695700</v>
+        <v>1755900</v>
       </c>
       <c r="G76" s="3">
-        <v>1271800</v>
+        <v>1317000</v>
       </c>
       <c r="H76" s="3">
-        <v>1230700</v>
+        <v>1274300</v>
       </c>
       <c r="I76" s="3">
-        <v>1381300</v>
+        <v>1430300</v>
       </c>
       <c r="J76" s="3">
-        <v>1594000</v>
+        <v>1650500</v>
       </c>
       <c r="K76" s="3">
         <v>1535200</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>262300</v>
+        <v>271600</v>
       </c>
       <c r="E81" s="3">
-        <v>-57200</v>
+        <v>-59300</v>
       </c>
       <c r="F81" s="3">
-        <v>276800</v>
+        <v>286700</v>
       </c>
       <c r="G81" s="3">
-        <v>-47800</v>
+        <v>-49500</v>
       </c>
       <c r="H81" s="3">
-        <v>-141900</v>
+        <v>-146900</v>
       </c>
       <c r="I81" s="3">
-        <v>-243400</v>
+        <v>-252100</v>
       </c>
       <c r="J81" s="3">
-        <v>19700</v>
+        <v>20400</v>
       </c>
       <c r="K81" s="3">
         <v>51700</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>188000</v>
+        <v>194600</v>
       </c>
       <c r="E83" s="3">
-        <v>200400</v>
+        <v>207500</v>
       </c>
       <c r="F83" s="3">
-        <v>211000</v>
+        <v>218500</v>
       </c>
       <c r="G83" s="3">
-        <v>190900</v>
+        <v>197700</v>
       </c>
       <c r="H83" s="3">
-        <v>220600</v>
+        <v>228400</v>
       </c>
       <c r="I83" s="3">
-        <v>139900</v>
+        <v>144800</v>
       </c>
       <c r="J83" s="3">
-        <v>137100</v>
+        <v>141900</v>
       </c>
       <c r="K83" s="3">
         <v>118200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>541400</v>
+        <v>560600</v>
       </c>
       <c r="E89" s="3">
-        <v>376800</v>
+        <v>390200</v>
       </c>
       <c r="F89" s="3">
-        <v>499500</v>
+        <v>517200</v>
       </c>
       <c r="G89" s="3">
-        <v>257000</v>
+        <v>266100</v>
       </c>
       <c r="H89" s="3">
-        <v>254600</v>
+        <v>263700</v>
       </c>
       <c r="I89" s="3">
-        <v>211400</v>
+        <v>218900</v>
       </c>
       <c r="J89" s="3">
-        <v>207000</v>
+        <v>214400</v>
       </c>
       <c r="K89" s="3">
         <v>245900</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-415800</v>
+        <v>-430500</v>
       </c>
       <c r="E91" s="3">
-        <v>-338200</v>
+        <v>-350200</v>
       </c>
       <c r="F91" s="3">
-        <v>-279800</v>
+        <v>-289800</v>
       </c>
       <c r="G91" s="3">
-        <v>-196000</v>
+        <v>-203000</v>
       </c>
       <c r="H91" s="3">
-        <v>-274000</v>
+        <v>-283700</v>
       </c>
       <c r="I91" s="3">
-        <v>-248300</v>
+        <v>-257100</v>
       </c>
       <c r="J91" s="3">
-        <v>-211700</v>
+        <v>-219200</v>
       </c>
       <c r="K91" s="3">
         <v>-132800</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-576600</v>
+        <v>-597100</v>
       </c>
       <c r="E94" s="3">
-        <v>-337400</v>
+        <v>-349400</v>
       </c>
       <c r="F94" s="3">
-        <v>-460600</v>
+        <v>-476900</v>
       </c>
       <c r="G94" s="3">
-        <v>-193600</v>
+        <v>-200500</v>
       </c>
       <c r="H94" s="3">
-        <v>-261100</v>
+        <v>-270300</v>
       </c>
       <c r="I94" s="3">
-        <v>-439400</v>
+        <v>-455000</v>
       </c>
       <c r="J94" s="3">
-        <v>-184100</v>
+        <v>-190600</v>
       </c>
       <c r="K94" s="3">
         <v>-141600</v>
@@ -4227,13 +4227,13 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-8400</v>
+        <v>-8700</v>
       </c>
       <c r="E96" s="3">
-        <v>-23400</v>
+        <v>-24200</v>
       </c>
       <c r="F96" s="3">
-        <v>-37200</v>
+        <v>-38500</v>
       </c>
       <c r="G96" s="3">
         <v>-200</v>
@@ -4242,10 +4242,10 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-8400</v>
+        <v>-8700</v>
       </c>
       <c r="J96" s="3">
-        <v>-23900</v>
+        <v>-24700</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>65000</v>
+        <v>67300</v>
       </c>
       <c r="E100" s="3">
-        <v>-62600</v>
+        <v>-64900</v>
       </c>
       <c r="F100" s="3">
-        <v>-234000</v>
+        <v>-242200</v>
       </c>
       <c r="G100" s="3">
-        <v>234300</v>
+        <v>242600</v>
       </c>
       <c r="H100" s="3">
-        <v>20700</v>
+        <v>21400</v>
       </c>
       <c r="I100" s="3">
-        <v>202600</v>
+        <v>209800</v>
       </c>
       <c r="J100" s="3">
-        <v>-24500</v>
+        <v>-25400</v>
       </c>
       <c r="K100" s="3">
         <v>-95100</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-6900</v>
+        <v>-7200</v>
       </c>
       <c r="E101" s="3">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="F101" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="G101" s="3">
-        <v>-5800</v>
+        <v>-6000</v>
       </c>
       <c r="H101" s="3">
         <v>1400</v>
       </c>
       <c r="I101" s="3">
-        <v>-3900</v>
+        <v>-4100</v>
       </c>
       <c r="J101" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="K101" s="3">
         <v>1100</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>22800</v>
+        <v>23600</v>
       </c>
       <c r="E102" s="3">
-        <v>-20200</v>
+        <v>-20900</v>
       </c>
       <c r="F102" s="3">
-        <v>-192500</v>
+        <v>-199400</v>
       </c>
       <c r="G102" s="3">
-        <v>291900</v>
+        <v>302300</v>
       </c>
       <c r="H102" s="3">
-        <v>15600</v>
+        <v>16200</v>
       </c>
       <c r="I102" s="3">
-        <v>-29400</v>
+        <v>-30400</v>
       </c>
       <c r="J102" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="K102" s="3">
         <v>10300</v>

--- a/AAII_Financials/Yearly/HMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HMY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>HMY</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44742</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44377</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44012</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43646</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43281</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42916</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42551</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42185</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41820</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41455</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41090</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40724</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2776600</v>
+        <v>3362300</v>
       </c>
       <c r="E8" s="3">
-        <v>2403000</v>
+        <v>2616100</v>
       </c>
       <c r="F8" s="3">
-        <v>2351700</v>
+        <v>2605000</v>
       </c>
       <c r="G8" s="3">
-        <v>1648000</v>
+        <v>2924000</v>
       </c>
       <c r="H8" s="3">
-        <v>1516500</v>
+        <v>1685700</v>
       </c>
       <c r="I8" s="3">
-        <v>1152500</v>
+        <v>1905200</v>
       </c>
       <c r="J8" s="3">
+        <v>1491500</v>
+      </c>
+      <c r="K8" s="3">
         <v>1085500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>998800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>921000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>99700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>106900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>133900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>117500</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2226100</v>
+        <v>2175400</v>
       </c>
       <c r="E9" s="3">
-        <v>2111000</v>
+        <v>1883900</v>
       </c>
       <c r="F9" s="3">
-        <v>1917800</v>
+        <v>2052100</v>
       </c>
       <c r="G9" s="3">
-        <v>1457700</v>
+        <v>2113000</v>
       </c>
       <c r="H9" s="3">
-        <v>1393500</v>
+        <v>1288800</v>
       </c>
       <c r="I9" s="3">
-        <v>1017200</v>
+        <v>1463600</v>
       </c>
       <c r="J9" s="3">
+        <v>1129100</v>
+      </c>
+      <c r="K9" s="3">
         <v>1005700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>861500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>914800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>91300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>107400</v>
-      </c>
-      <c r="O9" s="3">
-        <v>106000</v>
       </c>
       <c r="P9" s="3">
         <v>106000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3">
+        <v>106000</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>550500</v>
+        <v>1186900</v>
       </c>
       <c r="E10" s="3">
-        <v>292000</v>
+        <v>732200</v>
       </c>
       <c r="F10" s="3">
-        <v>433900</v>
+        <v>553000</v>
       </c>
       <c r="G10" s="3">
-        <v>190300</v>
+        <v>811000</v>
       </c>
       <c r="H10" s="3">
-        <v>123000</v>
+        <v>396800</v>
       </c>
       <c r="I10" s="3">
-        <v>135200</v>
+        <v>441500</v>
       </c>
       <c r="J10" s="3">
+        <v>362400</v>
+      </c>
+      <c r="K10" s="3">
         <v>79800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>137300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>27800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11500</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>28500</v>
-      </c>
-      <c r="E12" s="3">
-        <v>12100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>10000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>11600</v>
+      <c r="D12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H12" s="3">
-        <v>8300</v>
-      </c>
-      <c r="I12" s="3">
-        <v>7600</v>
-      </c>
-      <c r="J12" s="3">
+        <v>300</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="3">
         <v>13600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3300</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,77 +979,83 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>3400</v>
+        <v>180000</v>
       </c>
       <c r="E14" s="3">
-        <v>252800</v>
+        <v>46400</v>
       </c>
       <c r="F14" s="3">
-        <v>76500</v>
+        <v>282200</v>
       </c>
       <c r="G14" s="3">
-        <v>6800</v>
+        <v>97500</v>
       </c>
       <c r="H14" s="3">
-        <v>229800</v>
+        <v>10800</v>
       </c>
       <c r="I14" s="3">
-        <v>311700</v>
+        <v>14700</v>
       </c>
       <c r="J14" s="3">
+        <v>411200</v>
+      </c>
+      <c r="K14" s="3">
         <v>105700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>222100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>10500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>17100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4200</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>254300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>183400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>271500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>202200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>562500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>187400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2389000</v>
+        <v>2574600</v>
       </c>
       <c r="E17" s="3">
-        <v>2445600</v>
+        <v>2196400</v>
       </c>
       <c r="F17" s="3">
-        <v>1978100</v>
+        <v>2372000</v>
       </c>
       <c r="G17" s="3">
-        <v>1670700</v>
+        <v>2429800</v>
       </c>
       <c r="H17" s="3">
-        <v>1659500</v>
+        <v>1659000</v>
       </c>
       <c r="I17" s="3">
-        <v>1420600</v>
+        <v>2078800</v>
       </c>
       <c r="J17" s="3">
+        <v>1392800</v>
+      </c>
+      <c r="K17" s="3">
         <v>1094500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>912100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1230900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>109200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>118900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>115800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>117300</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>387700</v>
+        <v>787700</v>
       </c>
       <c r="E18" s="3">
-        <v>-42500</v>
+        <v>419700</v>
       </c>
       <c r="F18" s="3">
-        <v>373500</v>
+        <v>233000</v>
       </c>
       <c r="G18" s="3">
-        <v>-22700</v>
+        <v>494200</v>
       </c>
       <c r="H18" s="3">
-        <v>-143000</v>
+        <v>26700</v>
       </c>
       <c r="I18" s="3">
-        <v>-268100</v>
+        <v>-173700</v>
       </c>
       <c r="J18" s="3">
+        <v>98700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-9000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>86700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-309900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-12000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>18100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>200</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>5600</v>
+        <v>-5000</v>
       </c>
       <c r="E20" s="3">
-        <v>-6100</v>
+        <v>38000</v>
       </c>
       <c r="F20" s="3">
-        <v>-1500</v>
+        <v>25000</v>
       </c>
       <c r="G20" s="3">
-        <v>10000</v>
+        <v>-42600</v>
       </c>
       <c r="H20" s="3">
-        <v>3400</v>
+        <v>50000</v>
       </c>
       <c r="I20" s="3">
-        <v>21500</v>
+        <v>8700</v>
       </c>
       <c r="J20" s="3">
+        <v>52500</v>
+      </c>
+      <c r="K20" s="3">
         <v>13900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>14300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>12900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6400</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>587700</v>
+        <v>1047000</v>
       </c>
       <c r="E21" s="3">
-        <v>158600</v>
+        <v>565100</v>
       </c>
       <c r="F21" s="3">
-        <v>590200</v>
+        <v>433000</v>
       </c>
       <c r="G21" s="3">
-        <v>184800</v>
+        <v>808300</v>
       </c>
       <c r="H21" s="3">
-        <v>88600</v>
+        <v>178900</v>
       </c>
       <c r="I21" s="3">
-        <v>-102000</v>
+        <v>380200</v>
       </c>
       <c r="J21" s="3">
+        <v>233600</v>
+      </c>
+      <c r="K21" s="3">
         <v>146600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>220500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-150900</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="N21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>36000</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>21000</v>
+        <v>12300</v>
       </c>
       <c r="E22" s="3">
-        <v>11000</v>
+        <v>19800</v>
       </c>
       <c r="F22" s="3">
-        <v>12400</v>
+        <v>11900</v>
       </c>
       <c r="G22" s="3">
-        <v>20800</v>
+        <v>15400</v>
       </c>
       <c r="H22" s="3">
-        <v>15200</v>
+        <v>21800</v>
       </c>
       <c r="I22" s="3">
-        <v>18600</v>
+        <v>19200</v>
       </c>
       <c r="J22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K22" s="3">
         <v>13200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>15800</v>
-      </c>
-      <c r="M22" s="3">
-        <v>700</v>
       </c>
       <c r="N22" s="3">
         <v>700</v>
       </c>
       <c r="O22" s="3">
+        <v>700</v>
+      </c>
+      <c r="P22" s="3">
         <v>1300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4300</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>372200</v>
+        <v>644800</v>
       </c>
       <c r="E23" s="3">
-        <v>-59600</v>
+        <v>350700</v>
       </c>
       <c r="F23" s="3">
-        <v>359600</v>
+        <v>-64600</v>
       </c>
       <c r="G23" s="3">
-        <v>-33500</v>
+        <v>447200</v>
       </c>
       <c r="H23" s="3">
-        <v>-154700</v>
+        <v>-34300</v>
       </c>
       <c r="I23" s="3">
-        <v>-265200</v>
+        <v>-194400</v>
       </c>
       <c r="J23" s="3">
+        <v>-343300</v>
+      </c>
+      <c r="K23" s="3">
         <v>-8300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>86100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-312700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>17100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2300</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>97100</v>
+        <v>168800</v>
       </c>
       <c r="E24" s="3">
-        <v>-2600</v>
+        <v>91500</v>
       </c>
       <c r="F24" s="3">
-        <v>70900</v>
+        <v>-2800</v>
       </c>
       <c r="G24" s="3">
-        <v>14400</v>
+        <v>88100</v>
       </c>
       <c r="H24" s="3">
-        <v>-7800</v>
+        <v>14700</v>
       </c>
       <c r="I24" s="3">
-        <v>-13200</v>
+        <v>-9800</v>
       </c>
       <c r="J24" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="K24" s="3">
         <v>-28700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>34400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-42000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>275200</v>
+        <v>475900</v>
       </c>
       <c r="E26" s="3">
-        <v>-57000</v>
+        <v>259200</v>
       </c>
       <c r="F26" s="3">
-        <v>288700</v>
+        <v>-61800</v>
       </c>
       <c r="G26" s="3">
-        <v>-47900</v>
+        <v>359000</v>
       </c>
       <c r="H26" s="3">
-        <v>-146900</v>
+        <v>-49000</v>
       </c>
       <c r="I26" s="3">
-        <v>-252100</v>
+        <v>-184600</v>
       </c>
       <c r="J26" s="3">
+        <v>-326200</v>
+      </c>
+      <c r="K26" s="3">
         <v>20400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>51700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-270700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-15400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>18200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6200</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>271600</v>
+        <v>470400</v>
       </c>
       <c r="E27" s="3">
-        <v>-59300</v>
+        <v>255900</v>
       </c>
       <c r="F27" s="3">
-        <v>286700</v>
+        <v>-64300</v>
       </c>
       <c r="G27" s="3">
-        <v>-49500</v>
+        <v>356400</v>
       </c>
       <c r="H27" s="3">
-        <v>-146900</v>
+        <v>-50600</v>
       </c>
       <c r="I27" s="3">
-        <v>-252100</v>
+        <v>-184600</v>
       </c>
       <c r="J27" s="3">
+        <v>-326200</v>
+      </c>
+      <c r="K27" s="3">
         <v>20400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>51700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-270700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-15400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>18200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6200</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1620,17 +1680,20 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>2100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>5100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-100</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5600</v>
+        <v>5000</v>
       </c>
       <c r="E32" s="3">
-        <v>6100</v>
+        <v>-38000</v>
       </c>
       <c r="F32" s="3">
-        <v>1500</v>
+        <v>-25000</v>
       </c>
       <c r="G32" s="3">
-        <v>-10000</v>
+        <v>42600</v>
       </c>
       <c r="H32" s="3">
-        <v>-3400</v>
+        <v>-50000</v>
       </c>
       <c r="I32" s="3">
-        <v>-21500</v>
+        <v>-8700</v>
       </c>
       <c r="J32" s="3">
+        <v>-52500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-13900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-14300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-12900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>271600</v>
+        <v>470400</v>
       </c>
       <c r="E33" s="3">
-        <v>-59300</v>
+        <v>255900</v>
       </c>
       <c r="F33" s="3">
-        <v>286700</v>
+        <v>-64300</v>
       </c>
       <c r="G33" s="3">
-        <v>-49500</v>
+        <v>356400</v>
       </c>
       <c r="H33" s="3">
-        <v>-146900</v>
+        <v>-50600</v>
       </c>
       <c r="I33" s="3">
-        <v>-252100</v>
+        <v>-184600</v>
       </c>
       <c r="J33" s="3">
+        <v>-326200</v>
+      </c>
+      <c r="K33" s="3">
         <v>20400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>51700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-270700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>23400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6100</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>271600</v>
+        <v>470400</v>
       </c>
       <c r="E35" s="3">
-        <v>-59300</v>
+        <v>255900</v>
       </c>
       <c r="F35" s="3">
-        <v>286700</v>
+        <v>-64300</v>
       </c>
       <c r="G35" s="3">
-        <v>-49500</v>
+        <v>356400</v>
       </c>
       <c r="H35" s="3">
-        <v>-146900</v>
+        <v>-50600</v>
       </c>
       <c r="I35" s="3">
-        <v>-252100</v>
+        <v>-184600</v>
       </c>
       <c r="J35" s="3">
+        <v>-326200</v>
+      </c>
+      <c r="K35" s="3">
         <v>20400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>51700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-270700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>23400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6100</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44742</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44377</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44012</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43646</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43281</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42916</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42551</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42185</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41820</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41455</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41090</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40724</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,53 +2072,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>161600</v>
+        <v>257100</v>
       </c>
       <c r="E41" s="3">
-        <v>137900</v>
+        <v>152200</v>
       </c>
       <c r="F41" s="3">
-        <v>158900</v>
+        <v>149500</v>
       </c>
       <c r="G41" s="3">
-        <v>358200</v>
+        <v>197500</v>
       </c>
       <c r="H41" s="3">
-        <v>56000</v>
+        <v>366400</v>
       </c>
       <c r="I41" s="3">
-        <v>39800</v>
+        <v>70300</v>
       </c>
       <c r="J41" s="3">
+        <v>51500</v>
+      </c>
+      <c r="K41" s="3">
         <v>70200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>68400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>63700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7200</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2076,324 +2165,348 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>124300</v>
+        <v>123200</v>
       </c>
       <c r="E43" s="3">
-        <v>85800</v>
+        <v>117100</v>
       </c>
       <c r="F43" s="3">
-        <v>85700</v>
+        <v>102700</v>
       </c>
       <c r="G43" s="3">
-        <v>69300</v>
+        <v>115700</v>
       </c>
       <c r="H43" s="3">
-        <v>56200</v>
+        <v>70800</v>
       </c>
       <c r="I43" s="3">
-        <v>59900</v>
+        <v>70600</v>
       </c>
       <c r="J43" s="3">
+        <v>77500</v>
+      </c>
+      <c r="K43" s="3">
         <v>52400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>34000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>43100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>21500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12300</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>184000</v>
+        <v>197400</v>
       </c>
       <c r="E44" s="3">
-        <v>158800</v>
+        <v>173300</v>
       </c>
       <c r="F44" s="3">
-        <v>143200</v>
+        <v>172100</v>
       </c>
       <c r="G44" s="3">
-        <v>136400</v>
+        <v>178100</v>
       </c>
       <c r="H44" s="3">
-        <v>110800</v>
+        <v>139500</v>
       </c>
       <c r="I44" s="3">
-        <v>99100</v>
+        <v>139200</v>
       </c>
       <c r="J44" s="3">
+        <v>128300</v>
+      </c>
+      <c r="K44" s="3">
         <v>63500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>63600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>77100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>19200</v>
+        <v>30600</v>
       </c>
       <c r="E45" s="3">
-        <v>39800</v>
+        <v>5800</v>
       </c>
       <c r="F45" s="3">
-        <v>94000</v>
+        <v>31700</v>
       </c>
       <c r="G45" s="3">
-        <v>9000</v>
+        <v>103100</v>
       </c>
       <c r="H45" s="3">
-        <v>23700</v>
+        <v>1000</v>
       </c>
       <c r="I45" s="3">
-        <v>36800</v>
+        <v>21900</v>
       </c>
       <c r="J45" s="3">
+        <v>39300</v>
+      </c>
+      <c r="K45" s="3">
         <v>92000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3300</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>489000</v>
+        <v>629800</v>
       </c>
       <c r="E46" s="3">
-        <v>422300</v>
+        <v>460700</v>
       </c>
       <c r="F46" s="3">
-        <v>481800</v>
+        <v>457800</v>
       </c>
       <c r="G46" s="3">
-        <v>572900</v>
+        <v>599100</v>
       </c>
       <c r="H46" s="3">
-        <v>246600</v>
+        <v>586000</v>
       </c>
       <c r="I46" s="3">
-        <v>235600</v>
+        <v>309900</v>
       </c>
       <c r="J46" s="3">
+        <v>304900</v>
+      </c>
+      <c r="K46" s="3">
         <v>278100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>189000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>188000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>27500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>28500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>46400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>31500</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>25000</v>
+        <v>13900</v>
       </c>
       <c r="E47" s="3">
-        <v>28100</v>
+        <v>10000</v>
       </c>
       <c r="F47" s="3">
-        <v>25800</v>
+        <v>7600</v>
       </c>
       <c r="G47" s="3">
-        <v>30100</v>
+        <v>8800</v>
       </c>
       <c r="H47" s="3">
-        <v>25000</v>
+        <v>12900</v>
       </c>
       <c r="I47" s="3">
-        <v>19600</v>
+        <v>12000</v>
       </c>
       <c r="J47" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K47" s="3">
         <v>13200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5100</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2100</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2338900</v>
+        <v>2265000</v>
       </c>
       <c r="E48" s="3">
-        <v>1852300</v>
+        <v>2203700</v>
       </c>
       <c r="F48" s="3">
-        <v>1893200</v>
+        <v>2008000</v>
       </c>
       <c r="G48" s="3">
-        <v>1644600</v>
+        <v>2354000</v>
       </c>
       <c r="H48" s="3">
-        <v>1563700</v>
+        <v>1682300</v>
       </c>
       <c r="I48" s="3">
-        <v>1746900</v>
+        <v>1964400</v>
       </c>
       <c r="J48" s="3">
+        <v>2258500</v>
+      </c>
+      <c r="K48" s="3">
         <v>1693000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1630000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1763100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>205000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>194900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>548700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>326300</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1900</v>
+        <v>1000</v>
       </c>
       <c r="E49" s="3">
-        <v>2700</v>
+        <v>1800</v>
       </c>
       <c r="F49" s="3">
-        <v>20600</v>
+        <v>2900</v>
       </c>
       <c r="G49" s="3">
-        <v>30200</v>
+        <v>25600</v>
       </c>
       <c r="H49" s="3">
-        <v>30000</v>
+        <v>30900</v>
       </c>
       <c r="I49" s="3">
-        <v>29000</v>
+        <v>37700</v>
       </c>
       <c r="J49" s="3">
+        <v>39700</v>
+      </c>
+      <c r="K49" s="3">
         <v>34000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>47400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>52800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>18400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>22700</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>370700</v>
+        <v>390400</v>
       </c>
       <c r="E52" s="3">
-        <v>332200</v>
+        <v>346600</v>
       </c>
       <c r="F52" s="3">
-        <v>328600</v>
+        <v>370500</v>
       </c>
       <c r="G52" s="3">
-        <v>240600</v>
+        <v>412800</v>
       </c>
       <c r="H52" s="3">
-        <v>204700</v>
+        <v>215500</v>
       </c>
       <c r="I52" s="3">
-        <v>196000</v>
+        <v>257200</v>
       </c>
       <c r="J52" s="3">
+        <v>253900</v>
+      </c>
+      <c r="K52" s="3">
         <v>172800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>141400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>147300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>20200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>33900</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3225500</v>
+        <v>3312000</v>
       </c>
       <c r="E54" s="3">
-        <v>2637600</v>
+        <v>3038900</v>
       </c>
       <c r="F54" s="3">
-        <v>2750000</v>
+        <v>2859300</v>
       </c>
       <c r="G54" s="3">
-        <v>2518400</v>
+        <v>3419400</v>
       </c>
       <c r="H54" s="3">
-        <v>2070100</v>
+        <v>2576000</v>
       </c>
       <c r="I54" s="3">
-        <v>2227100</v>
+        <v>2600600</v>
       </c>
       <c r="J54" s="3">
+        <v>2882200</v>
+      </c>
+      <c r="K54" s="3">
         <v>2191100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2017400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2156300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>253400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>250800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>360700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>416400</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>67900</v>
+        <v>62300</v>
       </c>
       <c r="E57" s="3">
-        <v>71300</v>
+        <v>64000</v>
       </c>
       <c r="F57" s="3">
-        <v>71500</v>
+        <v>262500</v>
       </c>
       <c r="G57" s="3">
-        <v>39800</v>
+        <v>307500</v>
       </c>
       <c r="H57" s="3">
-        <v>43000</v>
+        <v>40700</v>
       </c>
       <c r="I57" s="3">
-        <v>33100</v>
+        <v>54000</v>
       </c>
       <c r="J57" s="3">
+        <v>42800</v>
+      </c>
+      <c r="K57" s="3">
         <v>29400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>31300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3700</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>18000</v>
+        <v>14700</v>
       </c>
       <c r="E58" s="3">
-        <v>12500</v>
+        <v>16900</v>
       </c>
       <c r="F58" s="3">
-        <v>27800</v>
+        <v>13600</v>
       </c>
       <c r="G58" s="3">
-        <v>17800</v>
+        <v>27100</v>
       </c>
       <c r="H58" s="3">
-        <v>5000</v>
+        <v>18200</v>
       </c>
       <c r="I58" s="3">
-        <v>38900</v>
+        <v>6300</v>
       </c>
       <c r="J58" s="3">
+        <v>50300</v>
+      </c>
+      <c r="K58" s="3">
         <v>103300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16300</v>
       </c>
-      <c r="L58" s="3" t="s">
+      <c r="M58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>1700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3500</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>301100</v>
+        <v>208500</v>
       </c>
       <c r="E59" s="3">
-        <v>196500</v>
+        <v>175800</v>
       </c>
       <c r="F59" s="3">
-        <v>213600</v>
+        <v>27900</v>
       </c>
       <c r="G59" s="3">
-        <v>368500</v>
+        <v>54400</v>
       </c>
       <c r="H59" s="3">
-        <v>134200</v>
+        <v>259600</v>
       </c>
       <c r="I59" s="3">
-        <v>130800</v>
+        <v>34800</v>
       </c>
       <c r="J59" s="3">
+        <v>28200</v>
+      </c>
+      <c r="K59" s="3">
         <v>83900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>75100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>67800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14700</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>387000</v>
+        <v>403100</v>
       </c>
       <c r="E60" s="3">
-        <v>280300</v>
+        <v>364600</v>
       </c>
       <c r="F60" s="3">
-        <v>312900</v>
+        <v>303900</v>
       </c>
       <c r="G60" s="3">
-        <v>426000</v>
+        <v>389100</v>
       </c>
       <c r="H60" s="3">
-        <v>182200</v>
+        <v>435800</v>
       </c>
       <c r="I60" s="3">
-        <v>202800</v>
+        <v>228900</v>
       </c>
       <c r="J60" s="3">
+        <v>262500</v>
+      </c>
+      <c r="K60" s="3">
         <v>216600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>110600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>99100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>20400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21900</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>332600</v>
+        <v>111300</v>
       </c>
       <c r="E61" s="3">
-        <v>193000</v>
+        <v>313300</v>
       </c>
       <c r="F61" s="3">
-        <v>176300</v>
+        <v>209200</v>
       </c>
       <c r="G61" s="3">
-        <v>425100</v>
+        <v>208400</v>
       </c>
       <c r="H61" s="3">
-        <v>328300</v>
+        <v>434800</v>
       </c>
       <c r="I61" s="3">
-        <v>277500</v>
+        <v>412400</v>
       </c>
       <c r="J61" s="3">
+        <v>359100</v>
+      </c>
+      <c r="K61" s="3">
         <v>16800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>111100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>202800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>17800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12800</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>540500</v>
+        <v>376900</v>
       </c>
       <c r="E62" s="3">
-        <v>467200</v>
+        <v>367800</v>
       </c>
       <c r="F62" s="3">
-        <v>502000</v>
+        <v>386500</v>
       </c>
       <c r="G62" s="3">
-        <v>350100</v>
+        <v>433600</v>
       </c>
       <c r="H62" s="3">
-        <v>285200</v>
+        <v>289600</v>
       </c>
       <c r="I62" s="3">
-        <v>316600</v>
+        <v>295400</v>
       </c>
       <c r="J62" s="3">
+        <v>312500</v>
+      </c>
+      <c r="K62" s="3">
         <v>307100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>260500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>258000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>31800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>31200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>43200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>66600</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1266900</v>
+        <v>1068800</v>
       </c>
       <c r="E66" s="3">
-        <v>944900</v>
+        <v>1187100</v>
       </c>
       <c r="F66" s="3">
-        <v>994200</v>
+        <v>1019600</v>
       </c>
       <c r="G66" s="3">
-        <v>1201400</v>
+        <v>1232400</v>
       </c>
       <c r="H66" s="3">
-        <v>795800</v>
+        <v>1228700</v>
       </c>
       <c r="I66" s="3">
-        <v>796800</v>
+        <v>999700</v>
       </c>
       <c r="J66" s="3">
+        <v>1031100</v>
+      </c>
+      <c r="K66" s="3">
         <v>540500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>482200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>559900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>61000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>58800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>76100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>101300</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-116700</v>
+        <v>122600</v>
       </c>
       <c r="E72" s="3">
-        <v>-387100</v>
+        <v>-263100</v>
       </c>
       <c r="F72" s="3">
-        <v>-312500</v>
+        <v>-588800</v>
       </c>
       <c r="G72" s="3">
-        <v>-569800</v>
+        <v>-572600</v>
       </c>
       <c r="H72" s="3">
-        <v>-531100</v>
+        <v>-725300</v>
       </c>
       <c r="I72" s="3">
-        <v>-397200</v>
+        <v>-829000</v>
       </c>
       <c r="J72" s="3">
+        <v>-663900</v>
+      </c>
+      <c r="K72" s="3">
         <v>-158100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-168800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-260800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>29500</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1958600</v>
+        <v>2233600</v>
       </c>
       <c r="E76" s="3">
-        <v>1692700</v>
+        <v>1845300</v>
       </c>
       <c r="F76" s="3">
-        <v>1755900</v>
+        <v>1835000</v>
       </c>
       <c r="G76" s="3">
-        <v>1317000</v>
+        <v>2183200</v>
       </c>
       <c r="H76" s="3">
-        <v>1274300</v>
+        <v>1347100</v>
       </c>
       <c r="I76" s="3">
-        <v>1430300</v>
+        <v>1600900</v>
       </c>
       <c r="J76" s="3">
+        <v>1851000</v>
+      </c>
+      <c r="K76" s="3">
         <v>1650500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1535200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1596400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>192400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>191900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>284600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>315100</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44742</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44377</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44012</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43646</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43281</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42916</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42551</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42185</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41820</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41455</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41090</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40724</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>271600</v>
+        <v>470400</v>
       </c>
       <c r="E81" s="3">
-        <v>-59300</v>
+        <v>255900</v>
       </c>
       <c r="F81" s="3">
-        <v>286700</v>
+        <v>-64300</v>
       </c>
       <c r="G81" s="3">
-        <v>-49500</v>
+        <v>356400</v>
       </c>
       <c r="H81" s="3">
-        <v>-146900</v>
+        <v>-50600</v>
       </c>
       <c r="I81" s="3">
-        <v>-252100</v>
+        <v>-184600</v>
       </c>
       <c r="J81" s="3">
+        <v>-326200</v>
+      </c>
+      <c r="K81" s="3">
         <v>20400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>51700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-270700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>23400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6100</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>194600</v>
+        <v>254300</v>
       </c>
       <c r="E83" s="3">
-        <v>207500</v>
+        <v>183400</v>
       </c>
       <c r="F83" s="3">
-        <v>218500</v>
+        <v>225000</v>
       </c>
       <c r="G83" s="3">
-        <v>197700</v>
+        <v>271600</v>
       </c>
       <c r="H83" s="3">
-        <v>228400</v>
+        <v>201900</v>
       </c>
       <c r="I83" s="3">
-        <v>144800</v>
+        <v>287000</v>
       </c>
       <c r="J83" s="3">
+        <v>187400</v>
+      </c>
+      <c r="K83" s="3">
         <v>141900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>118200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>147500</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>17500</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>560600</v>
+        <v>857300</v>
       </c>
       <c r="E89" s="3">
-        <v>390200</v>
+        <v>528200</v>
       </c>
       <c r="F89" s="3">
-        <v>517200</v>
+        <v>423000</v>
       </c>
       <c r="G89" s="3">
-        <v>266100</v>
+        <v>643100</v>
       </c>
       <c r="H89" s="3">
-        <v>263700</v>
+        <v>272200</v>
       </c>
       <c r="I89" s="3">
-        <v>218900</v>
+        <v>331200</v>
       </c>
       <c r="J89" s="3">
+        <v>283200</v>
+      </c>
+      <c r="K89" s="3">
         <v>214400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>245900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>119700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>14400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>19400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>37400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>24100</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-430500</v>
+        <v>-460000</v>
       </c>
       <c r="E91" s="3">
-        <v>-350200</v>
+        <v>-405600</v>
       </c>
       <c r="F91" s="3">
-        <v>-289800</v>
+        <v>-379600</v>
       </c>
       <c r="G91" s="3">
-        <v>-203000</v>
+        <v>-360300</v>
       </c>
       <c r="H91" s="3">
-        <v>-283700</v>
+        <v>-208100</v>
       </c>
       <c r="I91" s="3">
-        <v>-257100</v>
+        <v>-356500</v>
       </c>
       <c r="J91" s="3">
+        <v>-332700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-219200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-132800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-168400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-25400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-28200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-31900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-597100</v>
+        <v>-458000</v>
       </c>
       <c r="E94" s="3">
-        <v>-349400</v>
+        <v>-562600</v>
       </c>
       <c r="F94" s="3">
-        <v>-476900</v>
+        <v>-378700</v>
       </c>
       <c r="G94" s="3">
-        <v>-200500</v>
+        <v>-593000</v>
       </c>
       <c r="H94" s="3">
-        <v>-270300</v>
+        <v>-205100</v>
       </c>
       <c r="I94" s="3">
-        <v>-455000</v>
+        <v>-339600</v>
       </c>
       <c r="J94" s="3">
+        <v>-588900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-190600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-141600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-173500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-25400</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,35 +4453,36 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-8700</v>
+        <v>76400</v>
       </c>
       <c r="E96" s="3">
-        <v>-24200</v>
+        <v>7200</v>
       </c>
       <c r="F96" s="3">
-        <v>-38500</v>
+        <v>25300</v>
       </c>
       <c r="G96" s="3">
-        <v>-200</v>
+        <v>47400</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-8700</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>11200</v>
+      </c>
+      <c r="K96" s="3">
         <v>-24700</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4257,17 +4490,20 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-3000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>67300</v>
+        <v>-297700</v>
       </c>
       <c r="E100" s="3">
-        <v>-64900</v>
+        <v>63400</v>
       </c>
       <c r="F100" s="3">
-        <v>-242200</v>
+        <v>-70300</v>
       </c>
       <c r="G100" s="3">
-        <v>242600</v>
+        <v>-301200</v>
       </c>
       <c r="H100" s="3">
-        <v>21400</v>
+        <v>248100</v>
       </c>
       <c r="I100" s="3">
-        <v>209800</v>
+        <v>26900</v>
       </c>
       <c r="J100" s="3">
+        <v>271500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-25400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-95100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>8800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1700</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-7200</v>
+        <v>-1500</v>
       </c>
       <c r="E101" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="F101" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G101" s="3">
         <v>3200</v>
       </c>
-      <c r="F101" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-6000</v>
-      </c>
       <c r="H101" s="3">
-        <v>1400</v>
+        <v>-6100</v>
       </c>
       <c r="I101" s="3">
-        <v>-4100</v>
+        <v>1800</v>
       </c>
       <c r="J101" s="3">
-        <v>1100</v>
+        <v>-5300</v>
       </c>
       <c r="K101" s="3">
         <v>1100</v>
       </c>
       <c r="L101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2400</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="Q101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>23600</v>
+        <v>100000</v>
       </c>
       <c r="E102" s="3">
-        <v>-20900</v>
+        <v>22200</v>
       </c>
       <c r="F102" s="3">
-        <v>-199400</v>
+        <v>-22700</v>
       </c>
       <c r="G102" s="3">
-        <v>302300</v>
+        <v>-247900</v>
       </c>
       <c r="H102" s="3">
-        <v>16200</v>
+        <v>309200</v>
       </c>
       <c r="I102" s="3">
-        <v>-30400</v>
+        <v>20300</v>
       </c>
       <c r="J102" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="K102" s="3">
         <v>-600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-45500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>100</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
